--- a/research/traditional_assets/database/data/nigeria/nigeria_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_retail_distributors.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1287851543826682</v>
+        <v>0.1284302989195202</v>
       </c>
       <c r="C2">
-        <v>34.45034501519677</v>
+        <v>34.23687065545553</v>
       </c>
       <c r="D2">
-        <v>33.06034501519677</v>
+        <v>33.15017065545553</v>
       </c>
       <c r="E2">
-        <v>-26</v>
+        <v>-25.6967</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3033</v>
       </c>
       <c r="G2">
         <v>1.39</v>
@@ -1445,28 +1445,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01525599</v>
       </c>
       <c r="N2">
-        <v>9.963333333333333</v>
+        <v>9.948077343333333</v>
       </c>
       <c r="O2">
-        <v>2.989</v>
+        <v>2.984423203</v>
       </c>
       <c r="P2">
-        <v>6.974333333333333</v>
+        <v>6.963654140333333</v>
       </c>
       <c r="Q2">
-        <v>11.24433333333333</v>
+        <v>11.23365414033333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1287851543826682</v>
+        <v>0.1293719181005255</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5827003981542198</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>653.0768133260007</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1284302989195202</v>
+        <v>0.1280754434563722</v>
       </c>
       <c r="C3">
-        <v>34.23687065545553</v>
+        <v>34.02388574178921</v>
       </c>
       <c r="D3">
-        <v>33.15017065545553</v>
+        <v>33.24048574178921</v>
       </c>
       <c r="E3">
-        <v>-25.6967</v>
+        <v>-25.3934</v>
       </c>
       <c r="F3">
-        <v>0.3033</v>
+        <v>0.6066</v>
       </c>
       <c r="G3">
         <v>1.39</v>
@@ -1527,28 +1527,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M3">
-        <v>0.01525599</v>
+        <v>0.03051198</v>
       </c>
       <c r="N3">
-        <v>9.948077343333333</v>
+        <v>9.932821353333333</v>
       </c>
       <c r="O3">
-        <v>2.984423203</v>
+        <v>2.979846406</v>
       </c>
       <c r="P3">
-        <v>6.963654140333333</v>
+        <v>6.952974947333333</v>
       </c>
       <c r="Q3">
-        <v>11.23365414033333</v>
+        <v>11.22297494733333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1293719181005255</v>
+        <v>0.1299706565881349</v>
       </c>
       <c r="T3">
-        <v>0.5827003981542198</v>
+        <v>0.5868750678644521</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>653.0768133260007</v>
+        <v>326.5384066630003</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1280754434563722</v>
+        <v>0.1277205879932242</v>
       </c>
       <c r="C4">
-        <v>34.02388574178921</v>
+        <v>33.81139428550065</v>
       </c>
       <c r="D4">
-        <v>33.24048574178921</v>
+        <v>33.33129428550065</v>
       </c>
       <c r="E4">
-        <v>-25.3934</v>
+        <v>-25.0901</v>
       </c>
       <c r="F4">
-        <v>0.6066</v>
+        <v>0.9098999999999999</v>
       </c>
       <c r="G4">
         <v>1.39</v>
@@ -1609,28 +1609,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M4">
-        <v>0.03051198</v>
+        <v>0.04576796999999999</v>
       </c>
       <c r="N4">
-        <v>9.932821353333333</v>
+        <v>9.917565363333333</v>
       </c>
       <c r="O4">
-        <v>2.979846406</v>
+        <v>2.975269609</v>
       </c>
       <c r="P4">
-        <v>6.952974947333333</v>
+        <v>6.942295754333333</v>
       </c>
       <c r="Q4">
-        <v>11.22297494733333</v>
+        <v>11.21229575433333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1299706565881349</v>
+        <v>0.1305817401992002</v>
       </c>
       <c r="T4">
-        <v>0.5868750678644521</v>
+        <v>0.5911358132388128</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>326.5384066630003</v>
+        <v>217.6922711086669</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1277205879932242</v>
+        <v>0.1273657325300762</v>
       </c>
       <c r="C5">
-        <v>33.81139428550065</v>
+        <v>33.59940034184621</v>
       </c>
       <c r="D5">
-        <v>33.33129428550065</v>
+        <v>33.42260034184621</v>
       </c>
       <c r="E5">
-        <v>-25.0901</v>
+        <v>-24.7868</v>
       </c>
       <c r="F5">
-        <v>0.9098999999999999</v>
+        <v>1.2132</v>
       </c>
       <c r="G5">
         <v>1.39</v>
@@ -1691,28 +1691,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M5">
-        <v>0.04576796999999999</v>
+        <v>0.06102396</v>
       </c>
       <c r="N5">
-        <v>9.917565363333333</v>
+        <v>9.902309373333333</v>
       </c>
       <c r="O5">
-        <v>2.975269609</v>
+        <v>2.970692812</v>
       </c>
       <c r="P5">
-        <v>6.942295754333333</v>
+        <v>6.931616561333334</v>
       </c>
       <c r="Q5">
-        <v>11.21229575433333</v>
+        <v>11.20161656133333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1305817401992002</v>
+        <v>0.1312055547188294</v>
       </c>
       <c r="T5">
-        <v>0.5911358132388128</v>
+        <v>0.5954853241418061</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>217.6922711086669</v>
+        <v>163.2692033315002</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1273657325300762</v>
+        <v>0.1270108770669282</v>
       </c>
       <c r="C6">
-        <v>33.59940034184621</v>
+        <v>33.38790801063925</v>
       </c>
       <c r="D6">
-        <v>33.42260034184621</v>
+        <v>33.51440801063925</v>
       </c>
       <c r="E6">
-        <v>-24.7868</v>
+        <v>-24.4835</v>
       </c>
       <c r="F6">
-        <v>1.2132</v>
+        <v>1.5165</v>
       </c>
       <c r="G6">
         <v>1.39</v>
@@ -1773,28 +1773,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M6">
-        <v>0.06102396</v>
+        <v>0.07627995</v>
       </c>
       <c r="N6">
-        <v>9.902309373333333</v>
+        <v>9.887053383333333</v>
       </c>
       <c r="O6">
-        <v>2.970692812</v>
+        <v>2.966116015</v>
       </c>
       <c r="P6">
-        <v>6.931616561333334</v>
+        <v>6.920937368333333</v>
       </c>
       <c r="Q6">
-        <v>11.20161656133333</v>
+        <v>11.19093736833333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1312055547188294</v>
+        <v>0.1318425021757139</v>
       </c>
       <c r="T6">
-        <v>0.5954853241418061</v>
+        <v>0.5999264036953886</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>163.2692033315002</v>
+        <v>130.6153626652001</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1270108770669282</v>
+        <v>0.1266560216037802</v>
       </c>
       <c r="C7">
-        <v>33.38790801063925</v>
+        <v>33.17692143686399</v>
       </c>
       <c r="D7">
-        <v>33.51440801063925</v>
+        <v>33.60672143686399</v>
       </c>
       <c r="E7">
-        <v>-24.4835</v>
+        <v>-24.1802</v>
       </c>
       <c r="F7">
-        <v>1.5165</v>
+        <v>1.8198</v>
       </c>
       <c r="G7">
         <v>1.39</v>
@@ -1855,28 +1855,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M7">
-        <v>0.07627995</v>
+        <v>0.09153594</v>
       </c>
       <c r="N7">
-        <v>9.887053383333333</v>
+        <v>9.871797393333333</v>
       </c>
       <c r="O7">
-        <v>2.966116015</v>
+        <v>2.961539218</v>
       </c>
       <c r="P7">
-        <v>6.920937368333333</v>
+        <v>6.910258175333333</v>
       </c>
       <c r="Q7">
-        <v>11.19093736833333</v>
+        <v>11.18025817533333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1318425021757139</v>
+        <v>0.1324930017061491</v>
       </c>
       <c r="T7">
-        <v>0.5999264036953886</v>
+        <v>0.6044619743033028</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>130.6153626652001</v>
+        <v>108.8461355543334</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1266560216037802</v>
+        <v>0.1263011661406322</v>
       </c>
       <c r="C8">
-        <v>33.17692143686399</v>
+        <v>32.96644481129917</v>
       </c>
       <c r="D8">
-        <v>33.60672143686399</v>
+        <v>33.69954481129917</v>
       </c>
       <c r="E8">
-        <v>-24.1802</v>
+        <v>-23.8769</v>
       </c>
       <c r="F8">
-        <v>1.8198</v>
+        <v>2.1231</v>
       </c>
       <c r="G8">
         <v>1.39</v>
@@ -1937,28 +1937,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M8">
-        <v>0.09153593999999998</v>
+        <v>0.10679193</v>
       </c>
       <c r="N8">
-        <v>9.871797393333333</v>
+        <v>9.856541403333333</v>
       </c>
       <c r="O8">
-        <v>2.961539218</v>
+        <v>2.956962421</v>
       </c>
       <c r="P8">
-        <v>6.910258175333333</v>
+        <v>6.899578982333333</v>
       </c>
       <c r="Q8">
-        <v>11.18025817533333</v>
+        <v>11.16957898233333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1324930017061491</v>
+        <v>0.133157490473798</v>
       </c>
       <c r="T8">
-        <v>0.6044619743033028</v>
+        <v>0.6090950840640754</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>108.8461355543335</v>
+        <v>93.29668761800012</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1263011661406322</v>
+        <v>0.1259463106774842</v>
       </c>
       <c r="C9">
-        <v>32.96644481129917</v>
+        <v>32.75648237115232</v>
       </c>
       <c r="D9">
-        <v>33.69954481129917</v>
+        <v>33.79288237115232</v>
       </c>
       <c r="E9">
-        <v>-23.8769</v>
+        <v>-23.5736</v>
       </c>
       <c r="F9">
-        <v>2.1231</v>
+        <v>2.4264</v>
       </c>
       <c r="G9">
         <v>1.39</v>
@@ -2019,28 +2019,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M9">
-        <v>0.10679193</v>
+        <v>0.12204792</v>
       </c>
       <c r="N9">
-        <v>9.856541403333333</v>
+        <v>9.841285413333333</v>
       </c>
       <c r="O9">
-        <v>2.956962421</v>
+        <v>2.952385624</v>
       </c>
       <c r="P9">
-        <v>6.899578982333333</v>
+        <v>6.888899789333333</v>
       </c>
       <c r="Q9">
-        <v>11.16957898233333</v>
+        <v>11.15889978933333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.133157490473798</v>
+        <v>0.1338364246494393</v>
       </c>
       <c r="T9">
-        <v>0.6090950840640754</v>
+        <v>0.6138289136022561</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>93.29668761800011</v>
+        <v>81.63460166575008</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1259463106774842</v>
+        <v>0.1255914552143362</v>
       </c>
       <c r="C10">
-        <v>32.75648237115232</v>
+        <v>32.54703840070449</v>
       </c>
       <c r="D10">
-        <v>33.79288237115232</v>
+        <v>33.88673840070449</v>
       </c>
       <c r="E10">
-        <v>-23.5736</v>
+        <v>-23.2703</v>
       </c>
       <c r="F10">
-        <v>2.4264</v>
+        <v>2.7297</v>
       </c>
       <c r="G10">
         <v>1.39</v>
@@ -2101,28 +2101,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M10">
-        <v>0.12204792</v>
+        <v>0.13730391</v>
       </c>
       <c r="N10">
-        <v>9.841285413333333</v>
+        <v>9.826029423333333</v>
       </c>
       <c r="O10">
-        <v>2.952385624</v>
+        <v>2.947808827</v>
       </c>
       <c r="P10">
-        <v>6.888899789333333</v>
+        <v>6.878220596333334</v>
       </c>
       <c r="Q10">
-        <v>11.15889978933333</v>
+        <v>11.14822059633333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1338364246494393</v>
+        <v>0.1345302804553145</v>
       </c>
       <c r="T10">
-        <v>0.6138289136022561</v>
+        <v>0.618666783350067</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>81.63460166575008</v>
+        <v>72.56409036955564</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1255914552143362</v>
+        <v>0.1252365997511882</v>
       </c>
       <c r="C11">
-        <v>32.54703840070449</v>
+        <v>32.33811723196576</v>
       </c>
       <c r="D11">
-        <v>33.88673840070449</v>
+        <v>33.98111723196576</v>
       </c>
       <c r="E11">
-        <v>-23.2703</v>
+        <v>-22.967</v>
       </c>
       <c r="F11">
-        <v>2.7297</v>
+        <v>3.032999999999999</v>
       </c>
       <c r="G11">
         <v>1.39</v>
@@ -2183,28 +2183,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M11">
-        <v>0.13730391</v>
+        <v>0.1525599</v>
       </c>
       <c r="N11">
-        <v>9.826029423333333</v>
+        <v>9.810773433333333</v>
       </c>
       <c r="O11">
-        <v>2.947808827</v>
+        <v>2.94323203</v>
       </c>
       <c r="P11">
-        <v>6.878220596333334</v>
+        <v>6.867541403333333</v>
       </c>
       <c r="Q11">
-        <v>11.14822059633333</v>
+        <v>11.13754140333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1345302804553145</v>
+        <v>0.135239555279098</v>
       </c>
       <c r="T11">
-        <v>0.618666783350067</v>
+        <v>0.623612161314496</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>72.56409036955564</v>
+        <v>65.30768133260008</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1252365997511882</v>
+        <v>0.1248817442880402</v>
       </c>
       <c r="C12">
-        <v>32.33811723196576</v>
+        <v>32.1297232453418</v>
       </c>
       <c r="D12">
-        <v>33.98111723196576</v>
+        <v>34.0760232453418</v>
       </c>
       <c r="E12">
-        <v>-22.967</v>
+        <v>-22.6637</v>
       </c>
       <c r="F12">
-        <v>3.033</v>
+        <v>3.3363</v>
       </c>
       <c r="G12">
         <v>1.39</v>
@@ -2265,28 +2265,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M12">
-        <v>0.1525599</v>
+        <v>0.16781589</v>
       </c>
       <c r="N12">
-        <v>9.810773433333333</v>
+        <v>9.795517443333333</v>
       </c>
       <c r="O12">
-        <v>2.94323203</v>
+        <v>2.938655233</v>
       </c>
       <c r="P12">
-        <v>6.867541403333333</v>
+        <v>6.856862210333333</v>
       </c>
       <c r="Q12">
-        <v>11.13754140333333</v>
+        <v>11.12686221033333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.135239555279098</v>
+        <v>0.1359647688629665</v>
       </c>
       <c r="T12">
-        <v>0.623612161314496</v>
+        <v>0.6286686713680133</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>65.30768133260007</v>
+        <v>59.37061939327279</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1248817442880402</v>
+        <v>0.1245268888248922</v>
       </c>
       <c r="C13">
-        <v>32.1297232453418</v>
+        <v>31.92186087031151</v>
       </c>
       <c r="D13">
-        <v>34.0760232453418</v>
+        <v>34.17146087031151</v>
       </c>
       <c r="E13">
-        <v>-22.6637</v>
+        <v>-22.3604</v>
       </c>
       <c r="F13">
-        <v>3.3363</v>
+        <v>3.6396</v>
       </c>
       <c r="G13">
         <v>1.39</v>
@@ -2347,28 +2347,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M13">
-        <v>0.16781589</v>
+        <v>0.18307188</v>
       </c>
       <c r="N13">
-        <v>9.795517443333333</v>
+        <v>9.780261453333333</v>
       </c>
       <c r="O13">
-        <v>2.938655233</v>
+        <v>2.934078436</v>
       </c>
       <c r="P13">
-        <v>6.856862210333333</v>
+        <v>6.846183017333333</v>
       </c>
       <c r="Q13">
-        <v>11.12686221033333</v>
+        <v>11.11618301733333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1359647688629665</v>
+        <v>0.1367064645737411</v>
       </c>
       <c r="T13">
-        <v>0.6286686713680133</v>
+        <v>0.6338401021045651</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>59.37061939327279</v>
+        <v>54.42306777716674</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1245268888248922</v>
+        <v>0.1241720333617442</v>
       </c>
       <c r="C14">
-        <v>31.92186087031151</v>
+        <v>31.71453458611624</v>
       </c>
       <c r="D14">
-        <v>34.17146087031151</v>
+        <v>34.26743458611625</v>
       </c>
       <c r="E14">
-        <v>-22.3604</v>
+        <v>-22.0571</v>
       </c>
       <c r="F14">
-        <v>3.6396</v>
+        <v>3.9429</v>
       </c>
       <c r="G14">
         <v>1.39</v>
@@ -2429,28 +2429,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M14">
-        <v>0.18307188</v>
+        <v>0.19832787</v>
       </c>
       <c r="N14">
-        <v>9.780261453333333</v>
+        <v>9.765005463333333</v>
       </c>
       <c r="O14">
-        <v>2.934078436</v>
+        <v>2.929501639</v>
       </c>
       <c r="P14">
-        <v>6.846183017333333</v>
+        <v>6.835503824333333</v>
       </c>
       <c r="Q14">
-        <v>11.11618301733333</v>
+        <v>11.10550382433333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1367064645737411</v>
+        <v>0.1374652107606255</v>
       </c>
       <c r="T14">
-        <v>0.6338401021045651</v>
+        <v>0.6391304163063249</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>54.42306777716674</v>
+        <v>50.2366779481539</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1241720333617442</v>
+        <v>0.1238171778985961</v>
       </c>
       <c r="C15">
-        <v>31.71453458611624</v>
+        <v>31.50774892246054</v>
       </c>
       <c r="D15">
-        <v>34.26743458611625</v>
+        <v>34.36394892246054</v>
       </c>
       <c r="E15">
-        <v>-22.0571</v>
+        <v>-21.7538</v>
       </c>
       <c r="F15">
-        <v>3.9429</v>
+        <v>4.2462</v>
       </c>
       <c r="G15">
         <v>1.39</v>
@@ -2511,28 +2511,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M15">
-        <v>0.19832787</v>
+        <v>0.21358386</v>
       </c>
       <c r="N15">
-        <v>9.765005463333333</v>
+        <v>9.749749473333333</v>
       </c>
       <c r="O15">
-        <v>2.929501639</v>
+        <v>2.924924842</v>
       </c>
       <c r="P15">
-        <v>6.835503824333333</v>
+        <v>6.824824631333334</v>
       </c>
       <c r="Q15">
-        <v>11.10550382433333</v>
+        <v>11.09482463133333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1374652107606255</v>
+        <v>0.1382416022076699</v>
       </c>
       <c r="T15">
-        <v>0.6391304163063249</v>
+        <v>0.6445437610709164</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>50.2366779481539</v>
+        <v>46.64834380900005</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1238171778985961</v>
+        <v>0.1234623224354481</v>
       </c>
       <c r="C16">
-        <v>31.50774892246054</v>
+        <v>31.30150846022474</v>
       </c>
       <c r="D16">
-        <v>34.36394892246054</v>
+        <v>34.46100846022474</v>
       </c>
       <c r="E16">
-        <v>-21.7538</v>
+        <v>-21.4505</v>
       </c>
       <c r="F16">
-        <v>4.2462</v>
+        <v>4.5495</v>
       </c>
       <c r="G16">
         <v>1.39</v>
@@ -2593,28 +2593,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M16">
-        <v>0.21358386</v>
+        <v>0.22883985</v>
       </c>
       <c r="N16">
-        <v>9.749749473333333</v>
+        <v>9.734493483333333</v>
       </c>
       <c r="O16">
-        <v>2.924924842</v>
+        <v>2.920348045</v>
       </c>
       <c r="P16">
-        <v>6.824824631333334</v>
+        <v>6.814145438333333</v>
       </c>
       <c r="Q16">
-        <v>11.09482463133333</v>
+        <v>11.08414543833333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1382416022076699</v>
+        <v>0.1390362616887625</v>
       </c>
       <c r="T16">
-        <v>0.6445437610709164</v>
+        <v>0.6500844786534983</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>46.64834380900005</v>
+        <v>43.53845422173338</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1234623224354481</v>
+        <v>0.1231074669723002</v>
       </c>
       <c r="C17">
-        <v>31.30150846022474</v>
+        <v>31.09581783218983</v>
       </c>
       <c r="D17">
-        <v>34.46100846022474</v>
+        <v>34.55861783218983</v>
       </c>
       <c r="E17">
-        <v>-21.4505</v>
+        <v>-21.1472</v>
       </c>
       <c r="F17">
-        <v>4.549499999999999</v>
+        <v>4.8528</v>
       </c>
       <c r="G17">
         <v>1.39</v>
@@ -2675,28 +2675,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M17">
-        <v>0.22883985</v>
+        <v>0.24409584</v>
       </c>
       <c r="N17">
-        <v>9.734493483333333</v>
+        <v>9.719237493333333</v>
       </c>
       <c r="O17">
-        <v>2.920348045</v>
+        <v>2.915771248</v>
       </c>
       <c r="P17">
-        <v>6.814145438333333</v>
+        <v>6.803466245333333</v>
       </c>
       <c r="Q17">
-        <v>11.08414543833333</v>
+        <v>11.07346624533333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1390362616887625</v>
+        <v>0.1398498416336907</v>
       </c>
       <c r="T17">
-        <v>0.6500844786534983</v>
+        <v>0.6557571180832845</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>43.53845422173339</v>
+        <v>40.81730083287504</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1231074669723002</v>
+        <v>0.1227526115091521</v>
       </c>
       <c r="C18">
-        <v>31.09581783218983</v>
+        <v>30.89068172377453</v>
       </c>
       <c r="D18">
-        <v>34.55861783218983</v>
+        <v>34.65678172377453</v>
       </c>
       <c r="E18">
-        <v>-21.1472</v>
+        <v>-20.8439</v>
       </c>
       <c r="F18">
-        <v>4.8528</v>
+        <v>5.1561</v>
       </c>
       <c r="G18">
         <v>1.39</v>
@@ -2757,28 +2757,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M18">
-        <v>0.24409584</v>
+        <v>0.25935183</v>
       </c>
       <c r="N18">
-        <v>9.719237493333333</v>
+        <v>9.703981503333333</v>
       </c>
       <c r="O18">
-        <v>2.915771248</v>
+        <v>2.911194451</v>
       </c>
       <c r="P18">
-        <v>6.803466245333333</v>
+        <v>6.792787052333333</v>
       </c>
       <c r="Q18">
-        <v>11.07346624533333</v>
+        <v>11.06278705233333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1398498416336907</v>
+        <v>0.1406830259146411</v>
       </c>
       <c r="T18">
-        <v>0.6557571180832845</v>
+        <v>0.6615664476198125</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>40.81730083287504</v>
+        <v>38.41628313682357</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1227526115091521</v>
+        <v>0.1223977560460041</v>
       </c>
       <c r="C19">
-        <v>30.89068172377453</v>
+        <v>30.686104873785</v>
       </c>
       <c r="D19">
-        <v>34.65678172377453</v>
+        <v>34.755504873785</v>
       </c>
       <c r="E19">
-        <v>-20.8439</v>
+        <v>-20.5406</v>
       </c>
       <c r="F19">
-        <v>5.1561</v>
+        <v>5.4594</v>
       </c>
       <c r="G19">
         <v>1.39</v>
@@ -2839,28 +2839,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M19">
-        <v>0.25935183</v>
+        <v>0.27460782</v>
       </c>
       <c r="N19">
-        <v>9.703981503333333</v>
+        <v>9.688725513333333</v>
       </c>
       <c r="O19">
-        <v>2.911194451</v>
+        <v>2.906617654</v>
       </c>
       <c r="P19">
-        <v>6.792787052333333</v>
+        <v>6.782107859333333</v>
       </c>
       <c r="Q19">
-        <v>11.06278705233333</v>
+        <v>11.05210785933333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1406830259146411</v>
+        <v>0.1415365317634197</v>
       </c>
       <c r="T19">
-        <v>0.6615664476198125</v>
+        <v>0.6675174681206461</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>38.41628313682357</v>
+        <v>36.28204518477781</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1223977560460042</v>
+        <v>0.1220429005828561</v>
       </c>
       <c r="C20">
-        <v>30.686104873785</v>
+        <v>30.48209207517742</v>
       </c>
       <c r="D20">
-        <v>34.755504873785</v>
+        <v>34.85479207517742</v>
       </c>
       <c r="E20">
-        <v>-20.5406</v>
+        <v>-20.2373</v>
       </c>
       <c r="F20">
-        <v>5.4594</v>
+        <v>5.7627</v>
       </c>
       <c r="G20">
         <v>1.39</v>
@@ -2921,28 +2921,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M20">
-        <v>0.2746078199999999</v>
+        <v>0.2898638099999999</v>
       </c>
       <c r="N20">
-        <v>9.688725513333333</v>
+        <v>9.673469523333333</v>
       </c>
       <c r="O20">
-        <v>2.906617654</v>
+        <v>2.902040857</v>
       </c>
       <c r="P20">
-        <v>6.782107859333333</v>
+        <v>6.771428666333334</v>
       </c>
       <c r="Q20">
-        <v>11.05210785933333</v>
+        <v>11.04142866633333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1415365317634197</v>
+        <v>0.1424111118306866</v>
       </c>
       <c r="T20">
-        <v>0.6675174681206461</v>
+        <v>0.673615427399278</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>36.28204518477782</v>
+        <v>34.3724638592632</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1220429005828561</v>
+        <v>0.1216880451197081</v>
       </c>
       <c r="C21">
-        <v>30.48209207517742</v>
+        <v>30.27864817583366</v>
       </c>
       <c r="D21">
-        <v>34.85479207517742</v>
+        <v>34.95464817583366</v>
       </c>
       <c r="E21">
-        <v>-20.2373</v>
+        <v>-19.934</v>
       </c>
       <c r="F21">
-        <v>5.7627</v>
+        <v>6.066</v>
       </c>
       <c r="G21">
         <v>1.39</v>
@@ -3003,28 +3003,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M21">
-        <v>0.2898638099999999</v>
+        <v>0.3051198</v>
       </c>
       <c r="N21">
-        <v>9.673469523333333</v>
+        <v>9.658213533333333</v>
       </c>
       <c r="O21">
-        <v>2.902040857</v>
+        <v>2.89746406</v>
       </c>
       <c r="P21">
-        <v>6.771428666333334</v>
+        <v>6.760749473333333</v>
       </c>
       <c r="Q21">
-        <v>11.04142866633333</v>
+        <v>11.03074947333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1424111118306866</v>
+        <v>0.1433075563996352</v>
       </c>
       <c r="T21">
-        <v>0.673615427399278</v>
+        <v>0.6798658356598758</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>34.3724638592632</v>
+        <v>32.65384066630003</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1216880451197081</v>
+        <v>0.1213331896565601</v>
       </c>
       <c r="C22">
-        <v>30.27864817583366</v>
+        <v>30.07577807935034</v>
       </c>
       <c r="D22">
-        <v>34.95464817583366</v>
+        <v>35.05507807935034</v>
       </c>
       <c r="E22">
-        <v>-19.934</v>
+        <v>-19.6307</v>
       </c>
       <c r="F22">
-        <v>6.066</v>
+        <v>6.3693</v>
       </c>
       <c r="G22">
         <v>1.39</v>
@@ -3085,28 +3085,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M22">
-        <v>0.3051198</v>
+        <v>0.32037579</v>
       </c>
       <c r="N22">
-        <v>9.658213533333333</v>
+        <v>9.642957543333333</v>
       </c>
       <c r="O22">
-        <v>2.89746406</v>
+        <v>2.892887263</v>
       </c>
       <c r="P22">
-        <v>6.760749473333333</v>
+        <v>6.750070280333333</v>
       </c>
       <c r="Q22">
-        <v>11.03074947333333</v>
+        <v>11.02007028033333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1433075563996352</v>
+        <v>0.1442266957677976</v>
       </c>
       <c r="T22">
-        <v>0.6798658356598758</v>
+        <v>0.6862744821042862</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>32.65384066630003</v>
+        <v>31.0988958726667</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1213331896565601</v>
+        <v>0.1209783341934121</v>
       </c>
       <c r="C23">
-        <v>30.07577807935034</v>
+        <v>29.8734867458415</v>
       </c>
       <c r="D23">
-        <v>35.05507807935034</v>
+        <v>35.1560867458415</v>
       </c>
       <c r="E23">
-        <v>-19.6307</v>
+        <v>-19.3274</v>
       </c>
       <c r="F23">
-        <v>6.369299999999999</v>
+        <v>6.6726</v>
       </c>
       <c r="G23">
         <v>1.39</v>
@@ -3167,28 +3167,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M23">
-        <v>0.3203757899999999</v>
+        <v>0.33563178</v>
       </c>
       <c r="N23">
-        <v>9.642957543333333</v>
+        <v>9.627701553333333</v>
       </c>
       <c r="O23">
-        <v>2.892887263</v>
+        <v>2.888310466</v>
       </c>
       <c r="P23">
-        <v>6.750070280333333</v>
+        <v>6.739391087333333</v>
       </c>
       <c r="Q23">
-        <v>11.02007028033333</v>
+        <v>11.00939108733333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1442266957677976</v>
+        <v>0.1451694028120668</v>
       </c>
       <c r="T23">
-        <v>0.6862744821042861</v>
+        <v>0.692847452816502</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>31.09889587266671</v>
+        <v>29.68530969663639</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1209783341934121</v>
+        <v>0.1206234787302641</v>
       </c>
       <c r="C24">
-        <v>29.8734867458415</v>
+        <v>29.67177919275526</v>
       </c>
       <c r="D24">
-        <v>35.1560867458415</v>
+        <v>35.25767919275525</v>
       </c>
       <c r="E24">
-        <v>-19.3274</v>
+        <v>-19.0241</v>
       </c>
       <c r="F24">
-        <v>6.6726</v>
+        <v>6.9759</v>
       </c>
       <c r="G24">
         <v>1.39</v>
@@ -3249,28 +3249,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M24">
-        <v>0.33563178</v>
+        <v>0.35088777</v>
       </c>
       <c r="N24">
-        <v>9.627701553333333</v>
+        <v>9.612445563333333</v>
       </c>
       <c r="O24">
-        <v>2.888310466</v>
+        <v>2.883733669</v>
       </c>
       <c r="P24">
-        <v>6.739391087333333</v>
+        <v>6.728711894333333</v>
       </c>
       <c r="Q24">
-        <v>11.00939108733333</v>
+        <v>10.99871189433333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1451694028120668</v>
+        <v>0.1461365957535898</v>
       </c>
       <c r="T24">
-        <v>0.692847452816502</v>
+        <v>0.6995911500407233</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>29.68530969663639</v>
+        <v>28.3946440576522</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1206234787302641</v>
+        <v>0.1202686232671161</v>
       </c>
       <c r="C25">
-        <v>29.67177919275526</v>
+        <v>29.47066049570451</v>
       </c>
       <c r="D25">
-        <v>35.25767919275525</v>
+        <v>35.35986049570451</v>
       </c>
       <c r="E25">
-        <v>-19.0241</v>
+        <v>-18.7208</v>
       </c>
       <c r="F25">
-        <v>6.9759</v>
+        <v>7.2792</v>
       </c>
       <c r="G25">
         <v>1.39</v>
@@ -3331,28 +3331,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M25">
-        <v>0.35088777</v>
+        <v>0.36614376</v>
       </c>
       <c r="N25">
-        <v>9.612445563333333</v>
+        <v>9.597189573333333</v>
       </c>
       <c r="O25">
-        <v>2.883733669</v>
+        <v>2.879156872</v>
       </c>
       <c r="P25">
-        <v>6.728711894333333</v>
+        <v>6.718032701333334</v>
       </c>
       <c r="Q25">
-        <v>10.99871189433333</v>
+        <v>10.98803270133333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1461365957535898</v>
+        <v>0.1471292411409423</v>
       </c>
       <c r="T25">
-        <v>0.6995911500407233</v>
+        <v>0.7065123129813715</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>28.3946440576522</v>
+        <v>27.21153388858336</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1202686232671161</v>
+        <v>0.1199137678039681</v>
       </c>
       <c r="C26">
-        <v>29.47066049570451</v>
+        <v>29.27013578931237</v>
       </c>
       <c r="D26">
-        <v>35.35986049570451</v>
+        <v>35.46263578931237</v>
       </c>
       <c r="E26">
-        <v>-18.7208</v>
+        <v>-18.4175</v>
       </c>
       <c r="F26">
-        <v>7.279199999999999</v>
+        <v>7.5825</v>
       </c>
       <c r="G26">
         <v>1.39</v>
@@ -3413,28 +3413,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M26">
-        <v>0.3661437599999999</v>
+        <v>0.38139975</v>
       </c>
       <c r="N26">
-        <v>9.597189573333333</v>
+        <v>9.581933583333333</v>
       </c>
       <c r="O26">
-        <v>2.879156872</v>
+        <v>2.874580075</v>
       </c>
       <c r="P26">
-        <v>6.718032701333334</v>
+        <v>6.707353508333333</v>
       </c>
       <c r="Q26">
-        <v>10.98803270133333</v>
+        <v>10.97735350833333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1471292411409423</v>
+        <v>0.1481483570719575</v>
       </c>
       <c r="T26">
-        <v>0.7065123129813715</v>
+        <v>0.7136180402671037</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>27.21153388858337</v>
+        <v>26.12307253304003</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1199137678039681</v>
+        <v>0.1195589123408201</v>
       </c>
       <c r="C27">
-        <v>29.27013578931237</v>
+        <v>29.07021026807212</v>
       </c>
       <c r="D27">
-        <v>35.46263578931237</v>
+        <v>35.56601026807212</v>
       </c>
       <c r="E27">
-        <v>-18.4175</v>
+        <v>-18.1142</v>
       </c>
       <c r="F27">
-        <v>7.5825</v>
+        <v>7.8858</v>
       </c>
       <c r="G27">
         <v>1.39</v>
@@ -3495,28 +3495,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M27">
-        <v>0.38139975</v>
+        <v>0.39665574</v>
       </c>
       <c r="N27">
-        <v>9.581933583333333</v>
+        <v>9.566677593333333</v>
       </c>
       <c r="O27">
-        <v>2.874580075</v>
+        <v>2.870003278</v>
       </c>
       <c r="P27">
-        <v>6.707353508333333</v>
+        <v>6.696674315333333</v>
       </c>
       <c r="Q27">
-        <v>10.97735350833333</v>
+        <v>10.96667431533333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1481483570719575</v>
+        <v>0.1491950166767839</v>
       </c>
       <c r="T27">
-        <v>0.7136180402671037</v>
+        <v>0.720915814236234</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>26.12307253304003</v>
+        <v>25.11833897407695</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1195589123408201</v>
+        <v>0.1192040568776721</v>
       </c>
       <c r="C28">
-        <v>29.07021026807212</v>
+        <v>28.87088918722246</v>
       </c>
       <c r="D28">
-        <v>35.56601026807212</v>
+        <v>35.66998918722246</v>
       </c>
       <c r="E28">
-        <v>-18.1142</v>
+        <v>-17.8109</v>
       </c>
       <c r="F28">
-        <v>7.8858</v>
+        <v>8.1891</v>
       </c>
       <c r="G28">
         <v>1.39</v>
@@ -3577,28 +3577,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M28">
-        <v>0.39665574</v>
+        <v>0.41191173</v>
       </c>
       <c r="N28">
-        <v>9.566677593333333</v>
+        <v>9.551421603333333</v>
       </c>
       <c r="O28">
-        <v>2.870003278</v>
+        <v>2.865426481</v>
       </c>
       <c r="P28">
-        <v>6.696674315333333</v>
+        <v>6.685995122333333</v>
       </c>
       <c r="Q28">
-        <v>10.96667431533333</v>
+        <v>10.95599512233333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1491950166767839</v>
+        <v>0.1502703518872221</v>
       </c>
       <c r="T28">
-        <v>0.720915814236234</v>
+        <v>0.7284135272182174</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>25.11833897407695</v>
+        <v>24.18803012318521</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1192040568776721</v>
+        <v>0.1188492014145241</v>
       </c>
       <c r="C29">
-        <v>28.87088918722246</v>
+        <v>28.67217786363807</v>
       </c>
       <c r="D29">
-        <v>35.66998918722246</v>
+        <v>35.77457786363806</v>
       </c>
       <c r="E29">
-        <v>-17.8109</v>
+        <v>-17.5076</v>
       </c>
       <c r="F29">
-        <v>8.1891</v>
+        <v>8.4924</v>
       </c>
       <c r="G29">
         <v>1.39</v>
@@ -3659,28 +3659,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M29">
-        <v>0.41191173</v>
+        <v>0.42716772</v>
       </c>
       <c r="N29">
-        <v>9.551421603333333</v>
+        <v>9.536165613333333</v>
       </c>
       <c r="O29">
-        <v>2.865426481</v>
+        <v>2.860849684</v>
       </c>
       <c r="P29">
-        <v>6.685995122333333</v>
+        <v>6.675315929333333</v>
       </c>
       <c r="Q29">
-        <v>10.95599512233333</v>
+        <v>10.94531592933333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1502703518872221</v>
+        <v>0.1513755575201723</v>
       </c>
       <c r="T29">
-        <v>0.7284135272182174</v>
+        <v>0.7361195100052556</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>24.18803012318521</v>
+        <v>23.32417190450003</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1188492014145241</v>
+        <v>0.1184943459513761</v>
       </c>
       <c r="C30">
-        <v>28.67217786363807</v>
+        <v>28.47408167673578</v>
       </c>
       <c r="D30">
-        <v>35.77457786363806</v>
+        <v>35.87978167673578</v>
       </c>
       <c r="E30">
-        <v>-17.5076</v>
+        <v>-17.2043</v>
       </c>
       <c r="F30">
-        <v>8.4924</v>
+        <v>8.7957</v>
       </c>
       <c r="G30">
         <v>1.39</v>
@@ -3741,28 +3741,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M30">
-        <v>0.42716772</v>
+        <v>0.44242371</v>
       </c>
       <c r="N30">
-        <v>9.536165613333333</v>
+        <v>9.520909623333333</v>
       </c>
       <c r="O30">
-        <v>2.860849684</v>
+        <v>2.856272887</v>
       </c>
       <c r="P30">
-        <v>6.675315929333333</v>
+        <v>6.664636736333334</v>
       </c>
       <c r="Q30">
-        <v>10.94531592933333</v>
+        <v>10.93463673633333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1513755575201723</v>
+        <v>0.1525118957061635</v>
       </c>
       <c r="T30">
-        <v>0.7361195100052556</v>
+        <v>0.7440425627299571</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>23.32417190450003</v>
+        <v>22.51989011468968</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1184943459513761</v>
+        <v>0.1181394904882281</v>
       </c>
       <c r="C31">
-        <v>28.47408167673579</v>
+        <v>28.27660606939706</v>
       </c>
       <c r="D31">
-        <v>35.87978167673578</v>
+        <v>35.98560606939706</v>
       </c>
       <c r="E31">
-        <v>-17.2043</v>
+        <v>-16.901</v>
       </c>
       <c r="F31">
-        <v>8.795699999999998</v>
+        <v>9.098999999999998</v>
       </c>
       <c r="G31">
         <v>1.39</v>
@@ -3823,28 +3823,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M31">
-        <v>0.4424237099999999</v>
+        <v>0.4576796999999999</v>
       </c>
       <c r="N31">
-        <v>9.520909623333333</v>
+        <v>9.505653633333333</v>
       </c>
       <c r="O31">
-        <v>2.856272887</v>
+        <v>2.85169609</v>
       </c>
       <c r="P31">
-        <v>6.664636736333334</v>
+        <v>6.653957543333333</v>
       </c>
       <c r="Q31">
-        <v>10.93463673633333</v>
+        <v>10.92395754333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1525118957061635</v>
+        <v>0.1536807006974687</v>
       </c>
       <c r="T31">
-        <v>0.7440425627299571</v>
+        <v>0.7521919883896498</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>22.51989011468968</v>
+        <v>21.76922711086669</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1181394904882281</v>
+        <v>0.1177846350250801</v>
       </c>
       <c r="C32">
-        <v>28.27660606939706</v>
+        <v>28.07975654890656</v>
       </c>
       <c r="D32">
-        <v>35.98560606939706</v>
+        <v>36.09205654890656</v>
       </c>
       <c r="E32">
-        <v>-16.901</v>
+        <v>-16.5977</v>
       </c>
       <c r="F32">
-        <v>9.098999999999998</v>
+        <v>9.402299999999999</v>
       </c>
       <c r="G32">
         <v>1.39</v>
@@ -3905,28 +3905,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M32">
-        <v>0.4576796999999999</v>
+        <v>0.4729356899999999</v>
       </c>
       <c r="N32">
-        <v>9.505653633333333</v>
+        <v>9.490397643333333</v>
       </c>
       <c r="O32">
-        <v>2.85169609</v>
+        <v>2.847119293</v>
       </c>
       <c r="P32">
-        <v>6.653957543333333</v>
+        <v>6.643278350333333</v>
       </c>
       <c r="Q32">
-        <v>10.92395754333333</v>
+        <v>10.91327835033333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1536807006974687</v>
+        <v>0.154883384094319</v>
       </c>
       <c r="T32">
-        <v>0.7521919883896498</v>
+        <v>0.7605776292858555</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>21.76922711086669</v>
+        <v>21.06699397825809</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1177846350250801</v>
+        <v>0.1174297795619321</v>
       </c>
       <c r="C33">
-        <v>28.07975654890656</v>
+        <v>27.88353868790756</v>
       </c>
       <c r="D33">
-        <v>36.09205654890656</v>
+        <v>36.19913868790756</v>
       </c>
       <c r="E33">
-        <v>-16.5977</v>
+        <v>-16.2944</v>
       </c>
       <c r="F33">
-        <v>9.402299999999999</v>
+        <v>9.7056</v>
       </c>
       <c r="G33">
         <v>1.39</v>
@@ -3987,28 +3987,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M33">
-        <v>0.4729356899999999</v>
+        <v>0.48819168</v>
       </c>
       <c r="N33">
-        <v>9.490397643333333</v>
+        <v>9.475141653333333</v>
       </c>
       <c r="O33">
-        <v>2.847119293</v>
+        <v>2.842542496</v>
       </c>
       <c r="P33">
-        <v>6.643278350333333</v>
+        <v>6.632599157333333</v>
       </c>
       <c r="Q33">
-        <v>10.91327835033333</v>
+        <v>10.90259915733333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.154883384094319</v>
+        <v>0.156121440532253</v>
       </c>
       <c r="T33">
-        <v>0.7605776292858555</v>
+        <v>0.7692099066790085</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>21.06699397825809</v>
+        <v>20.40865041643752</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1174297795619321</v>
+        <v>0.1170749240987841</v>
       </c>
       <c r="C34">
-        <v>27.88353868790756</v>
+        <v>27.68795812537444</v>
       </c>
       <c r="D34">
-        <v>36.19913868790756</v>
+        <v>36.30685812537444</v>
       </c>
       <c r="E34">
-        <v>-16.2944</v>
+        <v>-15.9911</v>
       </c>
       <c r="F34">
-        <v>9.7056</v>
+        <v>10.0089</v>
       </c>
       <c r="G34">
         <v>1.39</v>
@@ -4069,28 +4069,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M34">
-        <v>0.48819168</v>
+        <v>0.50344767</v>
       </c>
       <c r="N34">
-        <v>9.475141653333333</v>
+        <v>9.459885663333333</v>
       </c>
       <c r="O34">
-        <v>2.842542496</v>
+        <v>2.837965699</v>
       </c>
       <c r="P34">
-        <v>6.632599157333333</v>
+        <v>6.621919964333333</v>
       </c>
       <c r="Q34">
-        <v>10.90259915733333</v>
+        <v>10.89191996433333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.156121440532253</v>
+        <v>0.1573964538787822</v>
       </c>
       <c r="T34">
-        <v>0.7692099066790085</v>
+        <v>0.7780998639943452</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>20.40865041643752</v>
+        <v>19.79020646442426</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1170749240987841</v>
+        <v>0.1167200686356361</v>
       </c>
       <c r="C35">
-        <v>27.68795812537444</v>
+        <v>27.49302056760251</v>
       </c>
       <c r="D35">
-        <v>36.30685812537444</v>
+        <v>36.41522056760251</v>
       </c>
       <c r="E35">
-        <v>-15.9911</v>
+        <v>-15.6878</v>
       </c>
       <c r="F35">
-        <v>10.0089</v>
+        <v>10.3122</v>
       </c>
       <c r="G35">
         <v>1.39</v>
@@ -4151,28 +4151,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M35">
-        <v>0.50344767</v>
+        <v>0.51870366</v>
       </c>
       <c r="N35">
-        <v>9.459885663333333</v>
+        <v>9.444629673333333</v>
       </c>
       <c r="O35">
-        <v>2.837965699</v>
+        <v>2.833388902</v>
       </c>
       <c r="P35">
-        <v>6.621919964333333</v>
+        <v>6.611240771333334</v>
       </c>
       <c r="Q35">
-        <v>10.89191996433333</v>
+        <v>10.88124077133333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1573964538787822</v>
+        <v>0.158710103993388</v>
       </c>
       <c r="T35">
-        <v>0.7780998639943452</v>
+        <v>0.7872592139556008</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>19.79020646442426</v>
+        <v>19.20814156841178</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1167200686356361</v>
+        <v>0.116365213172488</v>
       </c>
       <c r="C36">
-        <v>27.49302056760251</v>
+        <v>27.2987317892157</v>
       </c>
       <c r="D36">
-        <v>36.41522056760251</v>
+        <v>36.5242317892157</v>
       </c>
       <c r="E36">
-        <v>-15.6878</v>
+        <v>-15.3845</v>
       </c>
       <c r="F36">
-        <v>10.3122</v>
+        <v>10.6155</v>
       </c>
       <c r="G36">
         <v>1.39</v>
@@ -4233,28 +4233,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M36">
-        <v>0.51870366</v>
+        <v>0.53395965</v>
       </c>
       <c r="N36">
-        <v>9.444629673333333</v>
+        <v>9.429373683333333</v>
       </c>
       <c r="O36">
-        <v>2.833388902</v>
+        <v>2.828812105</v>
       </c>
       <c r="P36">
-        <v>6.611240771333334</v>
+        <v>6.600561578333333</v>
       </c>
       <c r="Q36">
-        <v>10.88124077133333</v>
+        <v>10.87056157833333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.158710103993388</v>
+        <v>0.1600641741115201</v>
       </c>
       <c r="T36">
-        <v>0.7872592139556008</v>
+        <v>0.7967003900695108</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>19.20814156841178</v>
+        <v>18.65933752360002</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.116365213172488</v>
+        <v>0.11601035770934</v>
       </c>
       <c r="C37">
-        <v>27.2987317892157</v>
+        <v>27.10509763419231</v>
       </c>
       <c r="D37">
-        <v>36.5242317892157</v>
+        <v>36.63389763419231</v>
       </c>
       <c r="E37">
-        <v>-15.3845</v>
+        <v>-15.0812</v>
       </c>
       <c r="F37">
-        <v>10.6155</v>
+        <v>10.9188</v>
       </c>
       <c r="G37">
         <v>1.39</v>
@@ -4315,28 +4315,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M37">
-        <v>0.53395965</v>
+        <v>0.54921564</v>
       </c>
       <c r="N37">
-        <v>9.429373683333333</v>
+        <v>9.414117693333333</v>
       </c>
       <c r="O37">
-        <v>2.828812105</v>
+        <v>2.824235308</v>
       </c>
       <c r="P37">
-        <v>6.600561578333333</v>
+        <v>6.589882385333333</v>
       </c>
       <c r="Q37">
-        <v>10.87056157833333</v>
+        <v>10.85988238533333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1600641741115201</v>
+        <v>0.1614605589208438</v>
       </c>
       <c r="T37">
-        <v>0.7967003900695108</v>
+        <v>0.8064366029369804</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>18.65933752360002</v>
+        <v>18.14102259238891</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.11601035770934</v>
+        <v>0.115655502246192</v>
       </c>
       <c r="C38">
-        <v>27.10509763419231</v>
+        <v>26.91212401690938</v>
       </c>
       <c r="D38">
-        <v>36.63389763419231</v>
+        <v>36.74422401690938</v>
       </c>
       <c r="E38">
-        <v>-15.0812</v>
+        <v>-14.7779</v>
       </c>
       <c r="F38">
-        <v>10.9188</v>
+        <v>11.2221</v>
       </c>
       <c r="G38">
         <v>1.39</v>
@@ -4397,28 +4397,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M38">
-        <v>0.5492156399999999</v>
+        <v>0.5644716299999999</v>
       </c>
       <c r="N38">
-        <v>9.414117693333333</v>
+        <v>9.398861703333333</v>
       </c>
       <c r="O38">
-        <v>2.824235308</v>
+        <v>2.819658511</v>
       </c>
       <c r="P38">
-        <v>6.589882385333333</v>
+        <v>6.579203192333333</v>
       </c>
       <c r="Q38">
-        <v>10.85988238533333</v>
+        <v>10.84920319233333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1614605589208438</v>
+        <v>0.162901273406654</v>
       </c>
       <c r="T38">
-        <v>0.8064366029369804</v>
+        <v>0.8164819019272267</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>18.14102259238891</v>
+        <v>17.65072468448651</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.115655502246192</v>
+        <v>0.115300646783044</v>
       </c>
       <c r="C39">
-        <v>26.91212401690938</v>
+        <v>26.71981692320596</v>
       </c>
       <c r="D39">
-        <v>36.74422401690938</v>
+        <v>36.85521692320596</v>
       </c>
       <c r="E39">
-        <v>-14.7779</v>
+        <v>-14.4746</v>
       </c>
       <c r="F39">
-        <v>11.2221</v>
+        <v>11.5254</v>
       </c>
       <c r="G39">
         <v>1.39</v>
@@ -4479,28 +4479,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M39">
-        <v>0.5644716299999999</v>
+        <v>0.5797276199999999</v>
       </c>
       <c r="N39">
-        <v>9.398861703333333</v>
+        <v>9.383605713333333</v>
       </c>
       <c r="O39">
-        <v>2.819658511</v>
+        <v>2.815081714</v>
       </c>
       <c r="P39">
-        <v>6.579203192333333</v>
+        <v>6.568523999333333</v>
       </c>
       <c r="Q39">
-        <v>10.84920319233333</v>
+        <v>10.83852399933333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.162901273406654</v>
+        <v>0.1643884625532968</v>
       </c>
       <c r="T39">
-        <v>0.8164819019272267</v>
+        <v>0.8268512428203842</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>17.65072468448651</v>
+        <v>17.1862319296316</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.115300646783044</v>
+        <v>0.114945791319896</v>
       </c>
       <c r="C40">
-        <v>26.71981692320596</v>
+        <v>26.52818241146567</v>
       </c>
       <c r="D40">
-        <v>36.85521692320596</v>
+        <v>36.96688241146567</v>
       </c>
       <c r="E40">
-        <v>-14.4746</v>
+        <v>-14.1713</v>
       </c>
       <c r="F40">
-        <v>11.5254</v>
+        <v>11.8287</v>
       </c>
       <c r="G40">
         <v>1.39</v>
@@ -4561,28 +4561,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M40">
-        <v>0.5797276199999999</v>
+        <v>0.59498361</v>
       </c>
       <c r="N40">
-        <v>9.383605713333333</v>
+        <v>9.368349723333333</v>
       </c>
       <c r="O40">
-        <v>2.815081714</v>
+        <v>2.810504917</v>
       </c>
       <c r="P40">
-        <v>6.568523999333333</v>
+        <v>6.557844806333334</v>
       </c>
       <c r="Q40">
-        <v>10.83852399933333</v>
+        <v>10.82784480633333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1643884625532968</v>
+        <v>0.1659244119998296</v>
       </c>
       <c r="T40">
-        <v>0.8268512428203842</v>
+        <v>0.8375605621034815</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>17.1862319296316</v>
+        <v>16.7455593160513</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.114945791319896</v>
+        <v>0.114590935856748</v>
       </c>
       <c r="C41">
-        <v>26.52818241146567</v>
+        <v>26.33722661371907</v>
       </c>
       <c r="D41">
-        <v>36.96688241146567</v>
+        <v>37.07922661371907</v>
       </c>
       <c r="E41">
-        <v>-14.1713</v>
+        <v>-13.868</v>
       </c>
       <c r="F41">
-        <v>11.8287</v>
+        <v>12.132</v>
       </c>
       <c r="G41">
         <v>1.39</v>
@@ -4643,28 +4643,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M41">
-        <v>0.59498361</v>
+        <v>0.6102396</v>
       </c>
       <c r="N41">
-        <v>9.368349723333333</v>
+        <v>9.353093733333333</v>
       </c>
       <c r="O41">
-        <v>2.810504917</v>
+        <v>2.80592812</v>
       </c>
       <c r="P41">
-        <v>6.557844806333334</v>
+        <v>6.547165613333333</v>
       </c>
       <c r="Q41">
-        <v>10.82784480633333</v>
+        <v>10.81716561333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1659244119998296</v>
+        <v>0.1675115597612467</v>
       </c>
       <c r="T41">
-        <v>0.8375605621034815</v>
+        <v>0.8486268586960153</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>16.7455593160513</v>
+        <v>16.32692033315002</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.114590935856748</v>
+        <v>0.1142360803936</v>
       </c>
       <c r="C42">
-        <v>26.33722661371907</v>
+        <v>26.14695573676613</v>
       </c>
       <c r="D42">
-        <v>37.07922661371907</v>
+        <v>37.19225573676613</v>
       </c>
       <c r="E42">
-        <v>-13.868</v>
+        <v>-13.5647</v>
       </c>
       <c r="F42">
-        <v>12.132</v>
+        <v>12.4353</v>
       </c>
       <c r="G42">
         <v>1.39</v>
@@ -4725,28 +4725,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M42">
-        <v>0.6102396</v>
+        <v>0.62549559</v>
       </c>
       <c r="N42">
-        <v>9.353093733333333</v>
+        <v>9.337837743333333</v>
       </c>
       <c r="O42">
-        <v>2.80592812</v>
+        <v>2.801351323</v>
       </c>
       <c r="P42">
-        <v>6.547165613333333</v>
+        <v>6.536486420333333</v>
       </c>
       <c r="Q42">
-        <v>10.81716561333333</v>
+        <v>10.80648642033333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1675115597612467</v>
+        <v>0.169152509141695</v>
       </c>
       <c r="T42">
-        <v>0.8486268586960153</v>
+        <v>0.860068283986601</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>16.32692033315002</v>
+        <v>15.9287027640488</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1142360803936</v>
+        <v>0.113881224930452</v>
       </c>
       <c r="C43">
-        <v>26.14695573676613</v>
+        <v>25.9573760633193</v>
       </c>
       <c r="D43">
-        <v>37.19225573676613</v>
+        <v>37.3059760633193</v>
       </c>
       <c r="E43">
-        <v>-13.5647</v>
+        <v>-13.2614</v>
       </c>
       <c r="F43">
-        <v>12.4353</v>
+        <v>12.7386</v>
       </c>
       <c r="G43">
         <v>1.39</v>
@@ -4807,28 +4807,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M43">
-        <v>0.62549559</v>
+        <v>0.64075158</v>
       </c>
       <c r="N43">
-        <v>9.337837743333333</v>
+        <v>9.322581753333333</v>
       </c>
       <c r="O43">
-        <v>2.801351323</v>
+        <v>2.796774526</v>
       </c>
       <c r="P43">
-        <v>6.536486420333333</v>
+        <v>6.525807227333333</v>
       </c>
       <c r="Q43">
-        <v>10.80648642033333</v>
+        <v>10.79580722733333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.169152509141695</v>
+        <v>0.170850042983538</v>
       </c>
       <c r="T43">
-        <v>0.860068283986601</v>
+        <v>0.8719042411837585</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>15.9287027640488</v>
+        <v>15.54944793633335</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.113881224930452</v>
+        <v>0.113526369467304</v>
       </c>
       <c r="C44">
-        <v>25.9573760633193</v>
+        <v>25.7684939531677</v>
       </c>
       <c r="D44">
-        <v>37.3059760633193</v>
+        <v>37.4203939531677</v>
       </c>
       <c r="E44">
-        <v>-13.2614</v>
+        <v>-12.9581</v>
       </c>
       <c r="F44">
-        <v>12.7386</v>
+        <v>13.0419</v>
       </c>
       <c r="G44">
         <v>1.39</v>
@@ -4889,28 +4889,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M44">
-        <v>0.6407515799999999</v>
+        <v>0.6560075699999999</v>
       </c>
       <c r="N44">
-        <v>9.322581753333333</v>
+        <v>9.307325763333333</v>
       </c>
       <c r="O44">
-        <v>2.796774526</v>
+        <v>2.792197729</v>
       </c>
       <c r="P44">
-        <v>6.525807227333333</v>
+        <v>6.515128034333333</v>
       </c>
       <c r="Q44">
-        <v>10.79580722733333</v>
+        <v>10.78512803433333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.170850042983538</v>
+        <v>0.1726071394163228</v>
       </c>
       <c r="T44">
-        <v>0.8719042411837584</v>
+        <v>0.8841554951246761</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>15.54944793633335</v>
+        <v>15.18783286804653</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.113526369467304</v>
+        <v>0.113171514004156</v>
       </c>
       <c r="C45">
-        <v>25.7684939531677</v>
+        <v>25.58031584436264</v>
       </c>
       <c r="D45">
-        <v>37.4203939531677</v>
+        <v>37.53551584436264</v>
       </c>
       <c r="E45">
-        <v>-12.9581</v>
+        <v>-12.6548</v>
       </c>
       <c r="F45">
-        <v>13.0419</v>
+        <v>13.3452</v>
       </c>
       <c r="G45">
         <v>1.39</v>
@@ -4971,28 +4971,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M45">
-        <v>0.6560075699999999</v>
+        <v>0.67126356</v>
       </c>
       <c r="N45">
-        <v>9.307325763333333</v>
+        <v>9.292069773333333</v>
       </c>
       <c r="O45">
-        <v>2.792197729</v>
+        <v>2.787620932</v>
       </c>
       <c r="P45">
-        <v>6.515128034333333</v>
+        <v>6.504448841333334</v>
       </c>
       <c r="Q45">
-        <v>10.78512803433333</v>
+        <v>10.77444884133333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1726071394163228</v>
+        <v>0.1744269892931357</v>
       </c>
       <c r="T45">
-        <v>0.8841554951246761</v>
+        <v>0.8968442938491978</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>15.18783286804653</v>
+        <v>14.8426548483182</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.113171514004156</v>
+        <v>0.112816658541008</v>
       </c>
       <c r="C46">
-        <v>25.58031584436264</v>
+        <v>25.3928482544253</v>
       </c>
       <c r="D46">
-        <v>37.53551584436264</v>
+        <v>37.65134825442529</v>
       </c>
       <c r="E46">
-        <v>-12.6548</v>
+        <v>-12.3515</v>
       </c>
       <c r="F46">
-        <v>13.3452</v>
+        <v>13.6485</v>
       </c>
       <c r="G46">
         <v>1.39</v>
@@ -5053,28 +5053,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M46">
-        <v>0.67126356</v>
+        <v>0.68651955</v>
       </c>
       <c r="N46">
-        <v>9.292069773333333</v>
+        <v>9.276813783333333</v>
       </c>
       <c r="O46">
-        <v>2.787620932</v>
+        <v>2.783044135</v>
       </c>
       <c r="P46">
-        <v>6.504448841333334</v>
+        <v>6.493769648333333</v>
       </c>
       <c r="Q46">
-        <v>10.77444884133333</v>
+        <v>10.76376964833333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1744269892931357</v>
+        <v>0.1763130155291055</v>
       </c>
       <c r="T46">
-        <v>0.8968442938491978</v>
+        <v>0.9099945034364295</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>14.8426548483182</v>
+        <v>14.51281807391113</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.112816658541008</v>
+        <v>0.11246180307786</v>
       </c>
       <c r="C47">
-        <v>25.3928482544253</v>
+        <v>25.20609778157658</v>
       </c>
       <c r="D47">
-        <v>37.65134825442529</v>
+        <v>37.76789778157658</v>
       </c>
       <c r="E47">
-        <v>-12.3515</v>
+        <v>-12.0482</v>
       </c>
       <c r="F47">
-        <v>13.6485</v>
+        <v>13.9518</v>
       </c>
       <c r="G47">
         <v>1.39</v>
@@ -5135,28 +5135,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M47">
-        <v>0.68651955</v>
+        <v>0.70177554</v>
       </c>
       <c r="N47">
-        <v>9.276813783333333</v>
+        <v>9.261557793333333</v>
       </c>
       <c r="O47">
-        <v>2.783044135</v>
+        <v>2.778467338</v>
       </c>
       <c r="P47">
-        <v>6.493769648333333</v>
+        <v>6.483090455333333</v>
       </c>
       <c r="Q47">
-        <v>10.76376964833333</v>
+        <v>10.75309045533333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1763130155291055</v>
+        <v>0.1782688945886296</v>
       </c>
       <c r="T47">
-        <v>0.9099945034364295</v>
+        <v>0.9236317578231882</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>14.51281807391113</v>
+        <v>14.1973220288261</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.11246180307786</v>
+        <v>0.112106947614712</v>
       </c>
       <c r="C48">
-        <v>25.20609778157658</v>
+        <v>25.02007110599012</v>
       </c>
       <c r="D48">
-        <v>37.76789778157658</v>
+        <v>37.88517110599012</v>
       </c>
       <c r="E48">
-        <v>-12.0482</v>
+        <v>-11.7449</v>
       </c>
       <c r="F48">
-        <v>13.9518</v>
+        <v>14.2551</v>
       </c>
       <c r="G48">
         <v>1.39</v>
@@ -5217,28 +5217,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M48">
-        <v>0.70177554</v>
+        <v>0.71703153</v>
       </c>
       <c r="N48">
-        <v>9.261557793333333</v>
+        <v>9.246301803333333</v>
       </c>
       <c r="O48">
-        <v>2.778467338</v>
+        <v>2.773890541</v>
       </c>
       <c r="P48">
-        <v>6.483090455333333</v>
+        <v>6.472411262333333</v>
       </c>
       <c r="Q48">
-        <v>10.75309045533333</v>
+        <v>10.74241126233333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1782688945886296</v>
+        <v>0.180298580405117</v>
       </c>
       <c r="T48">
-        <v>0.9236317578231882</v>
+        <v>0.9377836255830322</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>14.1973220288261</v>
+        <v>13.89525134736172</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.112106947614712</v>
+        <v>0.111752092151564</v>
       </c>
       <c r="C49">
-        <v>25.02007110599012</v>
+        <v>24.83477499106858</v>
       </c>
       <c r="D49">
-        <v>37.88517110599012</v>
+        <v>38.00317499106858</v>
       </c>
       <c r="E49">
-        <v>-11.7449</v>
+        <v>-11.4416</v>
       </c>
       <c r="F49">
-        <v>14.2551</v>
+        <v>14.5584</v>
       </c>
       <c r="G49">
         <v>1.39</v>
@@ -5299,28 +5299,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M49">
-        <v>0.71703153</v>
+        <v>0.73228752</v>
       </c>
       <c r="N49">
-        <v>9.246301803333333</v>
+        <v>9.231045813333333</v>
       </c>
       <c r="O49">
-        <v>2.773890541</v>
+        <v>2.769313744</v>
       </c>
       <c r="P49">
-        <v>6.472411262333333</v>
+        <v>6.461732069333333</v>
       </c>
       <c r="Q49">
-        <v>10.74241126233333</v>
+        <v>10.73173206933333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.180298580405117</v>
+        <v>0.1824063310607</v>
       </c>
       <c r="T49">
-        <v>0.9377836255830322</v>
+        <v>0.952479795949024</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>13.89525134736172</v>
+        <v>13.60576694429168</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.111752092151564</v>
+        <v>0.111397236688416</v>
       </c>
       <c r="C50">
-        <v>24.83477499106858</v>
+        <v>24.65021628474388</v>
       </c>
       <c r="D50">
-        <v>38.00317499106858</v>
+        <v>38.12191628474388</v>
       </c>
       <c r="E50">
-        <v>-11.4416</v>
+        <v>-11.1383</v>
       </c>
       <c r="F50">
-        <v>14.5584</v>
+        <v>14.8617</v>
       </c>
       <c r="G50">
         <v>1.39</v>
@@ -5381,28 +5381,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M50">
-        <v>0.7322875199999999</v>
+        <v>0.74754351</v>
       </c>
       <c r="N50">
-        <v>9.231045813333333</v>
+        <v>9.215789823333333</v>
       </c>
       <c r="O50">
-        <v>2.769313744</v>
+        <v>2.764736947</v>
       </c>
       <c r="P50">
-        <v>6.461732069333333</v>
+        <v>6.451052876333334</v>
       </c>
       <c r="Q50">
-        <v>10.73173206933333</v>
+        <v>10.72105287633333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1824063310607</v>
+        <v>0.1845967386047372</v>
       </c>
       <c r="T50">
-        <v>0.952479795949024</v>
+        <v>0.9677522867215252</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>13.60576694429168</v>
+        <v>13.32809823114287</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.111397236688416</v>
+        <v>0.111042381225268</v>
       </c>
       <c r="C51">
-        <v>24.65021628474388</v>
+        <v>24.46640192080194</v>
       </c>
       <c r="D51">
-        <v>38.12191628474388</v>
+        <v>38.24140192080194</v>
       </c>
       <c r="E51">
-        <v>-11.1383</v>
+        <v>-10.835</v>
       </c>
       <c r="F51">
-        <v>14.8617</v>
+        <v>15.165</v>
       </c>
       <c r="G51">
         <v>1.39</v>
@@ -5463,28 +5463,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M51">
-        <v>0.74754351</v>
+        <v>0.7627995</v>
       </c>
       <c r="N51">
-        <v>9.215789823333333</v>
+        <v>9.200533833333333</v>
       </c>
       <c r="O51">
-        <v>2.764736947</v>
+        <v>2.76016015</v>
       </c>
       <c r="P51">
-        <v>6.451052876333334</v>
+        <v>6.440373683333333</v>
       </c>
       <c r="Q51">
-        <v>10.72105287633333</v>
+        <v>10.71037368333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1845967386047372</v>
+        <v>0.186874762450536</v>
       </c>
       <c r="T51">
-        <v>0.9677522867215252</v>
+        <v>0.9836356771249267</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>13.32809823114287</v>
+        <v>13.06153626652001</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.111042381225268</v>
+        <v>0.11122302576212</v>
       </c>
       <c r="C52">
-        <v>24.46640192080194</v>
+        <v>24.10218250567175</v>
       </c>
       <c r="D52">
-        <v>38.24140192080194</v>
+        <v>38.18048250567175</v>
       </c>
       <c r="E52">
-        <v>-10.835</v>
+        <v>-10.5317</v>
       </c>
       <c r="F52">
-        <v>15.165</v>
+        <v>15.4683</v>
       </c>
       <c r="G52">
         <v>1.39</v>
@@ -5545,45 +5545,45 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M52">
-        <v>0.7627995</v>
+        <v>0.8012579399999999</v>
       </c>
       <c r="N52">
-        <v>9.200533833333333</v>
+        <v>9.162075393333334</v>
       </c>
       <c r="O52">
-        <v>2.76016015</v>
+        <v>2.748622618</v>
       </c>
       <c r="P52">
-        <v>6.440373683333333</v>
+        <v>6.413452775333333</v>
       </c>
       <c r="Q52">
-        <v>10.71037368333333</v>
+        <v>10.68345277533333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.186874762450536</v>
+        <v>0.1892457668614694</v>
       </c>
       <c r="T52">
-        <v>0.9836356771249267</v>
+        <v>1.000167369177447</v>
       </c>
       <c r="U52">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y52">
-        <v>13.06153626652001</v>
+        <v>12.43461416848279</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.11122302576212</v>
+        <v>0.110878670298972</v>
       </c>
       <c r="C53">
-        <v>24.10218250567175</v>
+        <v>23.91517891693324</v>
       </c>
       <c r="D53">
-        <v>38.18048250567175</v>
+        <v>38.29677891693323</v>
       </c>
       <c r="E53">
-        <v>-10.5317</v>
+        <v>-10.2284</v>
       </c>
       <c r="F53">
-        <v>15.4683</v>
+        <v>15.7716</v>
       </c>
       <c r="G53">
         <v>1.39</v>
@@ -5627,28 +5627,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M53">
-        <v>0.8012579399999999</v>
+        <v>0.8169688799999999</v>
       </c>
       <c r="N53">
-        <v>9.162075393333334</v>
+        <v>9.146364453333334</v>
       </c>
       <c r="O53">
-        <v>2.748622618</v>
+        <v>2.743909336</v>
       </c>
       <c r="P53">
-        <v>6.413452775333333</v>
+        <v>6.402455117333334</v>
       </c>
       <c r="Q53">
-        <v>10.68345277533333</v>
+        <v>10.67245511733333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1892457668614694</v>
+        <v>0.1917155631228583</v>
       </c>
       <c r="T53">
-        <v>1.000167369177447</v>
+        <v>1.017387881732155</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>12.43461416848279</v>
+        <v>12.19548697293505</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.110878670298972</v>
+        <v>0.110534314835824</v>
       </c>
       <c r="C54">
-        <v>23.91517891693324</v>
+        <v>23.72888596234509</v>
       </c>
       <c r="D54">
-        <v>38.29677891693323</v>
+        <v>38.41378596234509</v>
       </c>
       <c r="E54">
-        <v>-10.2284</v>
+        <v>-9.9251</v>
       </c>
       <c r="F54">
-        <v>15.7716</v>
+        <v>16.0749</v>
       </c>
       <c r="G54">
         <v>1.39</v>
@@ -5709,28 +5709,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M54">
-        <v>0.8169688799999999</v>
+        <v>0.83267982</v>
       </c>
       <c r="N54">
-        <v>9.146364453333334</v>
+        <v>9.130653513333334</v>
       </c>
       <c r="O54">
-        <v>2.743909336</v>
+        <v>2.739196054</v>
       </c>
       <c r="P54">
-        <v>6.402455117333334</v>
+        <v>6.391457459333333</v>
       </c>
       <c r="Q54">
-        <v>10.67245511733333</v>
+        <v>10.66145745933333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1917155631228583</v>
+        <v>0.1942904570974978</v>
       </c>
       <c r="T54">
-        <v>1.017387881732155</v>
+        <v>1.035341182055148</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>12.19548697293505</v>
+        <v>11.96538344514382</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.110534314835824</v>
+        <v>0.110189959372676</v>
       </c>
       <c r="C55">
-        <v>23.72888596234509</v>
+        <v>23.54331017540906</v>
       </c>
       <c r="D55">
-        <v>38.41378596234509</v>
+        <v>38.53151017540906</v>
       </c>
       <c r="E55">
-        <v>-9.9251</v>
+        <v>-9.6218</v>
       </c>
       <c r="F55">
-        <v>16.0749</v>
+        <v>16.3782</v>
       </c>
       <c r="G55">
         <v>1.39</v>
@@ -5791,28 +5791,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M55">
-        <v>0.83267982</v>
+        <v>0.8483907599999999</v>
       </c>
       <c r="N55">
-        <v>9.130653513333334</v>
+        <v>9.114942573333334</v>
       </c>
       <c r="O55">
-        <v>2.739196054</v>
+        <v>2.734482772</v>
       </c>
       <c r="P55">
-        <v>6.391457459333333</v>
+        <v>6.380459801333334</v>
       </c>
       <c r="Q55">
-        <v>10.66145745933333</v>
+        <v>10.65045980133333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1942904570974978</v>
+        <v>0.1969773029840782</v>
       </c>
       <c r="T55">
-        <v>1.035341182055148</v>
+        <v>1.054075060653054</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.96538344514382</v>
+        <v>11.74380227023375</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.110189959372676</v>
+        <v>0.109845603909528</v>
       </c>
       <c r="C56">
-        <v>23.54331017540906</v>
+        <v>23.35845816996432</v>
       </c>
       <c r="D56">
-        <v>38.53151017540906</v>
+        <v>38.64995816996432</v>
       </c>
       <c r="E56">
-        <v>-9.6218</v>
+        <v>-9.3185</v>
       </c>
       <c r="F56">
-        <v>16.3782</v>
+        <v>16.6815</v>
       </c>
       <c r="G56">
         <v>1.39</v>
@@ -5873,28 +5873,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M56">
-        <v>0.8483907599999999</v>
+        <v>0.8641017</v>
       </c>
       <c r="N56">
-        <v>9.114942573333334</v>
+        <v>9.099231633333332</v>
       </c>
       <c r="O56">
-        <v>2.734482772</v>
+        <v>2.729769489999999</v>
       </c>
       <c r="P56">
-        <v>6.380459801333334</v>
+        <v>6.369462143333333</v>
       </c>
       <c r="Q56">
-        <v>10.65045980133333</v>
+        <v>10.63946214333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1969773029840782</v>
+        <v>0.1997835642433955</v>
       </c>
       <c r="T56">
-        <v>1.054075060653054</v>
+        <v>1.073641556077535</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.74380227023375</v>
+        <v>11.53027859259313</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.109845603909528</v>
+        <v>0.10950124844638</v>
       </c>
       <c r="C57">
-        <v>23.35845816996432</v>
+        <v>23.17433664142602</v>
       </c>
       <c r="D57">
-        <v>38.64995816996432</v>
+        <v>38.76913664142602</v>
       </c>
       <c r="E57">
-        <v>-9.3185</v>
+        <v>-9.0152</v>
       </c>
       <c r="F57">
-        <v>16.6815</v>
+        <v>16.9848</v>
       </c>
       <c r="G57">
         <v>1.39</v>
@@ -5955,28 +5955,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M57">
-        <v>0.8641017</v>
+        <v>0.8798126399999999</v>
       </c>
       <c r="N57">
-        <v>9.099231633333332</v>
+        <v>9.083520693333334</v>
       </c>
       <c r="O57">
-        <v>2.729769489999999</v>
+        <v>2.725056208</v>
       </c>
       <c r="P57">
-        <v>6.369462143333333</v>
+        <v>6.358464485333334</v>
       </c>
       <c r="Q57">
-        <v>10.63946214333333</v>
+        <v>10.62846448533333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1997835642433955</v>
+        <v>0.2027173828326818</v>
       </c>
       <c r="T57">
-        <v>1.073641556077535</v>
+        <v>1.094097437657673</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>11.53027859259313</v>
+        <v>11.32438076058254</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.10950124844638</v>
+        <v>0.1091568929832319</v>
       </c>
       <c r="C58">
-        <v>23.17433664142602</v>
+        <v>22.99095236804688</v>
       </c>
       <c r="D58">
-        <v>38.76913664142602</v>
+        <v>38.88905236804688</v>
       </c>
       <c r="E58">
-        <v>-9.0152</v>
+        <v>-8.7119</v>
       </c>
       <c r="F58">
-        <v>16.9848</v>
+        <v>17.2881</v>
       </c>
       <c r="G58">
         <v>1.39</v>
@@ -6037,28 +6037,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M58">
-        <v>0.8798126399999999</v>
+        <v>0.89552358</v>
       </c>
       <c r="N58">
-        <v>9.083520693333334</v>
+        <v>9.067809753333332</v>
       </c>
       <c r="O58">
-        <v>2.725056208</v>
+        <v>2.720342925999999</v>
       </c>
       <c r="P58">
-        <v>6.358464485333334</v>
+        <v>6.347466827333333</v>
       </c>
       <c r="Q58">
-        <v>10.62846448533333</v>
+        <v>10.61746682733333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2027173828326818</v>
+        <v>0.2057876581005395</v>
       </c>
       <c r="T58">
-        <v>1.094097437657673</v>
+        <v>1.115504755590375</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>11.32438076058254</v>
+        <v>11.12570741390565</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1091568929832319</v>
+        <v>0.1088125375200839</v>
       </c>
       <c r="C59">
-        <v>22.99095236804688</v>
+        <v>22.80831221220237</v>
       </c>
       <c r="D59">
-        <v>38.88905236804688</v>
+        <v>39.00971221220237</v>
       </c>
       <c r="E59">
-        <v>-8.7119</v>
+        <v>-8.4086</v>
       </c>
       <c r="F59">
-        <v>17.2881</v>
+        <v>17.5914</v>
       </c>
       <c r="G59">
         <v>1.39</v>
@@ -6119,28 +6119,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M59">
-        <v>0.89552358</v>
+        <v>0.9112345199999999</v>
       </c>
       <c r="N59">
-        <v>9.067809753333332</v>
+        <v>9.052098813333332</v>
       </c>
       <c r="O59">
-        <v>2.720342925999999</v>
+        <v>2.715629643999999</v>
       </c>
       <c r="P59">
-        <v>6.347466827333333</v>
+        <v>6.336469169333332</v>
       </c>
       <c r="Q59">
-        <v>10.61746682733333</v>
+        <v>10.60646916933333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2057876581005395</v>
+        <v>0.2090041369525808</v>
       </c>
       <c r="T59">
-        <v>1.115504755590375</v>
+        <v>1.137931469615111</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>11.12570741390565</v>
+        <v>10.93388487228659</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1088125375200839</v>
+        <v>0.1084681820569359</v>
       </c>
       <c r="C60">
-        <v>22.80831221220237</v>
+        <v>22.62642312169968</v>
       </c>
       <c r="D60">
-        <v>39.00971221220237</v>
+        <v>39.13112312169968</v>
       </c>
       <c r="E60">
-        <v>-8.408600000000003</v>
+        <v>-8.105300000000003</v>
       </c>
       <c r="F60">
-        <v>17.5914</v>
+        <v>17.8947</v>
       </c>
       <c r="G60">
         <v>1.39</v>
@@ -6201,28 +6201,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M60">
-        <v>0.9112345199999998</v>
+        <v>0.9269454599999998</v>
       </c>
       <c r="N60">
-        <v>9.052098813333334</v>
+        <v>9.036387873333332</v>
       </c>
       <c r="O60">
-        <v>2.715629644</v>
+        <v>2.710916361999999</v>
       </c>
       <c r="P60">
-        <v>6.336469169333334</v>
+        <v>6.325471511333333</v>
       </c>
       <c r="Q60">
-        <v>10.60646916933333</v>
+        <v>10.59547151133333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2090041369525808</v>
+        <v>0.2123775172120389</v>
       </c>
       <c r="T60">
-        <v>1.137931469615111</v>
+        <v>1.161452169689834</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.93388487228659</v>
+        <v>10.74856478970546</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1084681820569359</v>
+        <v>0.1081238265937879</v>
       </c>
       <c r="C61">
-        <v>22.62642312169968</v>
+        <v>22.44529213111143</v>
       </c>
       <c r="D61">
-        <v>39.13112312169968</v>
+        <v>39.25329213111143</v>
       </c>
       <c r="E61">
-        <v>-8.105300000000003</v>
+        <v>-7.802000000000003</v>
       </c>
       <c r="F61">
-        <v>17.8947</v>
+        <v>18.198</v>
       </c>
       <c r="G61">
         <v>1.39</v>
@@ -6283,28 +6283,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M61">
-        <v>0.9269454599999998</v>
+        <v>0.9426563999999998</v>
       </c>
       <c r="N61">
-        <v>9.036387873333332</v>
+        <v>9.020676933333332</v>
       </c>
       <c r="O61">
-        <v>2.710916361999999</v>
+        <v>2.706203079999999</v>
       </c>
       <c r="P61">
-        <v>6.325471511333333</v>
+        <v>6.314473853333332</v>
       </c>
       <c r="Q61">
-        <v>10.59547151133333</v>
+        <v>10.58447385333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2123775172120389</v>
+        <v>0.2159195664844698</v>
       </c>
       <c r="T61">
-        <v>1.161452169689834</v>
+        <v>1.186148904768294</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.74856478970546</v>
+        <v>10.56942204321037</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1081238265937879</v>
+        <v>0.1077794711306399</v>
       </c>
       <c r="C62">
-        <v>22.44529213111143</v>
+        <v>22.26492636313427</v>
       </c>
       <c r="D62">
-        <v>39.25329213111143</v>
+        <v>39.37622636313426</v>
       </c>
       <c r="E62">
-        <v>-7.802000000000003</v>
+        <v>-7.498700000000003</v>
       </c>
       <c r="F62">
-        <v>18.198</v>
+        <v>18.5013</v>
       </c>
       <c r="G62">
         <v>1.39</v>
@@ -6365,28 +6365,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M62">
-        <v>0.9426563999999998</v>
+        <v>0.9583673399999998</v>
       </c>
       <c r="N62">
-        <v>9.020676933333332</v>
+        <v>9.004965993333332</v>
       </c>
       <c r="O62">
-        <v>2.706203079999999</v>
+        <v>2.701489797999999</v>
       </c>
       <c r="P62">
-        <v>6.314473853333332</v>
+        <v>6.303476195333333</v>
       </c>
       <c r="Q62">
-        <v>10.58447385333333</v>
+        <v>10.57347619533333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2159195664844698</v>
+        <v>0.2196432593093331</v>
       </c>
       <c r="T62">
-        <v>1.186148904768294</v>
+        <v>1.212112139081546</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.56942204321037</v>
+        <v>10.39615282938725</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1077794711306399</v>
+        <v>0.1074351156674919</v>
       </c>
       <c r="C63">
-        <v>22.26492636313427</v>
+        <v>22.08533302997315</v>
       </c>
       <c r="D63">
-        <v>39.37622636313426</v>
+        <v>39.49993302997314</v>
       </c>
       <c r="E63">
-        <v>-7.498700000000003</v>
+        <v>-7.195400000000003</v>
       </c>
       <c r="F63">
-        <v>18.5013</v>
+        <v>18.8046</v>
       </c>
       <c r="G63">
         <v>1.39</v>
@@ -6447,28 +6447,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M63">
-        <v>0.9583673399999998</v>
+        <v>0.9740782799999999</v>
       </c>
       <c r="N63">
-        <v>9.004965993333332</v>
+        <v>8.989255053333332</v>
       </c>
       <c r="O63">
-        <v>2.701489797999999</v>
+        <v>2.696776515999999</v>
       </c>
       <c r="P63">
-        <v>6.303476195333333</v>
+        <v>6.292478537333333</v>
       </c>
       <c r="Q63">
-        <v>10.57347619533333</v>
+        <v>10.56247853733333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2196432593093331</v>
+        <v>0.223562935967084</v>
       </c>
       <c r="T63">
-        <v>1.212112139081546</v>
+        <v>1.239441859411285</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>10.39615282938725</v>
+        <v>10.2284729450423</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1074351156674919</v>
+        <v>0.1070907602043439</v>
       </c>
       <c r="C64">
-        <v>22.08533302997315</v>
+        <v>21.90651943475185</v>
       </c>
       <c r="D64">
-        <v>39.49993302997314</v>
+        <v>39.62441943475185</v>
       </c>
       <c r="E64">
-        <v>-7.195400000000003</v>
+        <v>-6.892099999999999</v>
       </c>
       <c r="F64">
-        <v>18.8046</v>
+        <v>19.1079</v>
       </c>
       <c r="G64">
         <v>1.39</v>
@@ -6529,28 +6529,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M64">
-        <v>0.9740782799999999</v>
+        <v>0.98978922</v>
       </c>
       <c r="N64">
-        <v>8.989255053333332</v>
+        <v>8.973544113333332</v>
       </c>
       <c r="O64">
-        <v>2.696776515999999</v>
+        <v>2.692063233999999</v>
       </c>
       <c r="P64">
-        <v>6.292478537333333</v>
+        <v>6.281480879333333</v>
       </c>
       <c r="Q64">
-        <v>10.56247853733333</v>
+        <v>10.55148087933333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.223562935967084</v>
+        <v>0.2276944870387674</v>
       </c>
       <c r="T64">
-        <v>1.239441859411285</v>
+        <v>1.26824886192101</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>10.2284729450423</v>
+        <v>10.06611623162892</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1070907602043439</v>
+        <v>0.1067464047411959</v>
       </c>
       <c r="C65">
-        <v>21.90651943475185</v>
+        <v>21.72849297295014</v>
       </c>
       <c r="D65">
-        <v>39.62441943475185</v>
+        <v>39.74969297295014</v>
       </c>
       <c r="E65">
-        <v>-6.892099999999999</v>
+        <v>-6.588799999999999</v>
       </c>
       <c r="F65">
-        <v>19.1079</v>
+        <v>19.4112</v>
       </c>
       <c r="G65">
         <v>1.39</v>
@@ -6611,28 +6611,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M65">
-        <v>0.98978922</v>
+        <v>1.00550016</v>
       </c>
       <c r="N65">
-        <v>8.973544113333332</v>
+        <v>8.957833173333333</v>
       </c>
       <c r="O65">
-        <v>2.692063233999999</v>
+        <v>2.687349951999999</v>
       </c>
       <c r="P65">
-        <v>6.281480879333333</v>
+        <v>6.270483221333333</v>
       </c>
       <c r="Q65">
-        <v>10.55148087933333</v>
+        <v>10.54048322133333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2276944870387674</v>
+        <v>0.2320555687255442</v>
       </c>
       <c r="T65">
-        <v>1.26824886192101</v>
+        <v>1.298656253459054</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>10.06611623162892</v>
+        <v>9.908833165509723</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1067464047411959</v>
+        <v>0.1071755492780479</v>
       </c>
       <c r="C66">
-        <v>21.72849297295014</v>
+        <v>21.26919495687315</v>
       </c>
       <c r="D66">
-        <v>39.74969297295014</v>
+        <v>39.59369495687315</v>
       </c>
       <c r="E66">
-        <v>-6.588799999999999</v>
+        <v>-6.285499999999999</v>
       </c>
       <c r="F66">
-        <v>19.4112</v>
+        <v>19.7145</v>
       </c>
       <c r="G66">
         <v>1.39</v>
@@ -6693,45 +6693,45 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M66">
-        <v>1.00550016</v>
+        <v>1.05472575</v>
       </c>
       <c r="N66">
-        <v>8.957833173333333</v>
+        <v>8.908607583333334</v>
       </c>
       <c r="O66">
-        <v>2.687349951999999</v>
+        <v>2.672582275</v>
       </c>
       <c r="P66">
-        <v>6.270483221333333</v>
+        <v>6.236025308333334</v>
       </c>
       <c r="Q66">
-        <v>10.54048322133333</v>
+        <v>10.50602530833333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2320555687255442</v>
+        <v>0.2366658550801369</v>
       </c>
       <c r="T66">
-        <v>1.298656253459054</v>
+        <v>1.330801210227842</v>
       </c>
       <c r="U66">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>9.908833165509723</v>
+        <v>9.446373460905201</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1071755492780479</v>
+        <v>0.1068430938148999</v>
       </c>
       <c r="C67">
-        <v>21.26919495687315</v>
+        <v>21.08663841450627</v>
       </c>
       <c r="D67">
-        <v>39.59369495687315</v>
+        <v>39.71443841450627</v>
       </c>
       <c r="E67">
-        <v>-6.285499999999999</v>
+        <v>-5.982199999999999</v>
       </c>
       <c r="F67">
-        <v>19.7145</v>
+        <v>20.0178</v>
       </c>
       <c r="G67">
         <v>1.39</v>
@@ -6775,28 +6775,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M67">
-        <v>1.05472575</v>
+        <v>1.0709523</v>
       </c>
       <c r="N67">
-        <v>8.908607583333334</v>
+        <v>8.892381033333333</v>
       </c>
       <c r="O67">
-        <v>2.672582275</v>
+        <v>2.66771431</v>
       </c>
       <c r="P67">
-        <v>6.236025308333334</v>
+        <v>6.224666723333334</v>
       </c>
       <c r="Q67">
-        <v>10.50602530833333</v>
+        <v>10.49466672333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2366658550801369</v>
+        <v>0.2415473347497056</v>
       </c>
       <c r="T67">
-        <v>1.330801210227842</v>
+        <v>1.364837046806559</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>9.446373460905201</v>
+        <v>9.303246590285424</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1068430938148999</v>
+        <v>0.1065106383517519</v>
       </c>
       <c r="C68">
-        <v>21.08663841450627</v>
+        <v>20.90482055430058</v>
       </c>
       <c r="D68">
-        <v>39.71443841450627</v>
+        <v>39.83592055430059</v>
       </c>
       <c r="E68">
-        <v>-5.982199999999999</v>
+        <v>-5.678899999999999</v>
       </c>
       <c r="F68">
-        <v>20.0178</v>
+        <v>20.3211</v>
       </c>
       <c r="G68">
         <v>1.39</v>
@@ -6857,28 +6857,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M68">
-        <v>1.0709523</v>
+        <v>1.08717885</v>
       </c>
       <c r="N68">
-        <v>8.892381033333333</v>
+        <v>8.876154483333332</v>
       </c>
       <c r="O68">
-        <v>2.66771431</v>
+        <v>2.662846345</v>
       </c>
       <c r="P68">
-        <v>6.224666723333334</v>
+        <v>6.213308138333332</v>
       </c>
       <c r="Q68">
-        <v>10.49466672333333</v>
+        <v>10.48330813833333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2415473347497056</v>
+        <v>0.2467246616719755</v>
       </c>
       <c r="T68">
-        <v>1.364837046806559</v>
+        <v>1.400935661359744</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>9.303246590285424</v>
+        <v>9.164392163564745</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1065106383517519</v>
+        <v>0.1061781828886039</v>
       </c>
       <c r="C69">
-        <v>20.90482055430058</v>
+        <v>20.7237481756996</v>
       </c>
       <c r="D69">
-        <v>39.83592055430059</v>
+        <v>39.95814817569961</v>
       </c>
       <c r="E69">
-        <v>-5.678899999999999</v>
+        <v>-5.375599999999999</v>
       </c>
       <c r="F69">
-        <v>20.3211</v>
+        <v>20.6244</v>
       </c>
       <c r="G69">
         <v>1.39</v>
@@ -6939,28 +6939,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M69">
-        <v>1.08717885</v>
+        <v>1.1034054</v>
       </c>
       <c r="N69">
-        <v>8.876154483333332</v>
+        <v>8.859927933333333</v>
       </c>
       <c r="O69">
-        <v>2.662846345</v>
+        <v>2.65797838</v>
       </c>
       <c r="P69">
-        <v>6.213308138333332</v>
+        <v>6.201949553333334</v>
       </c>
       <c r="Q69">
-        <v>10.48330813833333</v>
+        <v>10.47194955333333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2467246616719755</v>
+        <v>0.2522255715268872</v>
       </c>
       <c r="T69">
-        <v>1.400935661359744</v>
+        <v>1.439290439322503</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>9.164392163564745</v>
+        <v>9.029621690571147</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1061781828886039</v>
+        <v>0.1058457274254559</v>
       </c>
       <c r="C70">
-        <v>20.7237481756996</v>
+        <v>20.54342816185392</v>
       </c>
       <c r="D70">
-        <v>39.95814817569961</v>
+        <v>40.08112816185393</v>
       </c>
       <c r="E70">
-        <v>-5.375599999999999</v>
+        <v>-5.072299999999998</v>
       </c>
       <c r="F70">
-        <v>20.6244</v>
+        <v>20.9277</v>
       </c>
       <c r="G70">
         <v>1.39</v>
@@ -7021,28 +7021,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M70">
-        <v>1.1034054</v>
+        <v>1.11963195</v>
       </c>
       <c r="N70">
-        <v>8.859927933333333</v>
+        <v>8.843701383333332</v>
       </c>
       <c r="O70">
-        <v>2.65797838</v>
+        <v>2.653110415</v>
       </c>
       <c r="P70">
-        <v>6.201949553333334</v>
+        <v>6.190590968333333</v>
       </c>
       <c r="Q70">
-        <v>10.47194955333333</v>
+        <v>10.46059096833333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2522255715268872</v>
+        <v>0.2580813787917932</v>
       </c>
       <c r="T70">
-        <v>1.439290439322503</v>
+        <v>1.480119719089311</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>9.029621690571147</v>
+        <v>8.8987576080991</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1058457274254559</v>
+        <v>0.1055132719623079</v>
       </c>
       <c r="C71">
-        <v>20.54342816185392</v>
+        <v>20.3638674809134</v>
       </c>
       <c r="D71">
-        <v>40.08112816185393</v>
+        <v>40.2048674809134</v>
       </c>
       <c r="E71">
-        <v>-5.072299999999998</v>
+        <v>-4.768999999999998</v>
       </c>
       <c r="F71">
-        <v>20.9277</v>
+        <v>21.231</v>
       </c>
       <c r="G71">
         <v>1.39</v>
@@ -7103,28 +7103,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M71">
-        <v>1.11963195</v>
+        <v>1.1358585</v>
       </c>
       <c r="N71">
-        <v>8.843701383333332</v>
+        <v>8.827474833333333</v>
       </c>
       <c r="O71">
-        <v>2.653110415</v>
+        <v>2.64824245</v>
       </c>
       <c r="P71">
-        <v>6.190590968333333</v>
+        <v>6.179232383333334</v>
       </c>
       <c r="Q71">
-        <v>10.46059096833333</v>
+        <v>10.44923238333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2580813787917932</v>
+        <v>0.264327573207693</v>
       </c>
       <c r="T71">
-        <v>1.480119719089311</v>
+        <v>1.523670950840573</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.8987576080991</v>
+        <v>8.771632499411972</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1055132719623079</v>
+        <v>0.1051808164991599</v>
       </c>
       <c r="C72">
-        <v>20.3638674809134</v>
+        <v>20.18507318734326</v>
       </c>
       <c r="D72">
-        <v>40.2048674809134</v>
+        <v>40.32937318734326</v>
       </c>
       <c r="E72">
-        <v>-4.768999999999998</v>
+        <v>-4.465699999999998</v>
       </c>
       <c r="F72">
-        <v>21.231</v>
+        <v>21.5343</v>
       </c>
       <c r="G72">
         <v>1.39</v>
@@ -7185,28 +7185,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M72">
-        <v>1.1358585</v>
+        <v>1.15208505</v>
       </c>
       <c r="N72">
-        <v>8.827474833333333</v>
+        <v>8.811248283333333</v>
       </c>
       <c r="O72">
-        <v>2.64824245</v>
+        <v>2.643374485</v>
       </c>
       <c r="P72">
-        <v>6.179232383333334</v>
+        <v>6.167873798333333</v>
       </c>
       <c r="Q72">
-        <v>10.44923238333333</v>
+        <v>10.43787379833333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.264327573207693</v>
+        <v>0.2710045396522756</v>
       </c>
       <c r="T72">
-        <v>1.523670950840573</v>
+        <v>1.57022571581606</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.771632499411972</v>
+        <v>8.648088379701942</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1051808164991599</v>
+        <v>0.1048483610360119</v>
       </c>
       <c r="C73">
-        <v>20.18507318734326</v>
+        <v>20.00705242326474</v>
       </c>
       <c r="D73">
-        <v>40.32937318734326</v>
+        <v>40.45465242326474</v>
       </c>
       <c r="E73">
-        <v>-4.465700000000002</v>
+        <v>-4.162400000000002</v>
       </c>
       <c r="F73">
-        <v>21.5343</v>
+        <v>21.8376</v>
       </c>
       <c r="G73">
         <v>1.39</v>
@@ -7267,28 +7267,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M73">
-        <v>1.15208505</v>
+        <v>1.1683116</v>
       </c>
       <c r="N73">
-        <v>8.811248283333333</v>
+        <v>8.795021733333334</v>
       </c>
       <c r="O73">
-        <v>2.643374485</v>
+        <v>2.63850652</v>
       </c>
       <c r="P73">
-        <v>6.167873798333333</v>
+        <v>6.156515213333334</v>
       </c>
       <c r="Q73">
-        <v>10.43787379833333</v>
+        <v>10.42651521333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2710045396522754</v>
+        <v>0.278158432271471</v>
       </c>
       <c r="T73">
-        <v>1.570225715816059</v>
+        <v>1.620105821146938</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.648088379701944</v>
+        <v>8.527976041094973</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1048483610360119</v>
+        <v>0.1045159055728639</v>
       </c>
       <c r="C74">
-        <v>20.00705242326474</v>
+        <v>19.82981241982079</v>
       </c>
       <c r="D74">
-        <v>40.45465242326474</v>
+        <v>40.58071241982079</v>
       </c>
       <c r="E74">
-        <v>-4.162400000000002</v>
+        <v>-3.859100000000002</v>
       </c>
       <c r="F74">
-        <v>21.8376</v>
+        <v>22.1409</v>
       </c>
       <c r="G74">
         <v>1.39</v>
@@ -7349,28 +7349,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M74">
-        <v>1.1683116</v>
+        <v>1.18453815</v>
       </c>
       <c r="N74">
-        <v>8.795021733333334</v>
+        <v>8.778795183333333</v>
       </c>
       <c r="O74">
-        <v>2.63850652</v>
+        <v>2.633638555</v>
       </c>
       <c r="P74">
-        <v>6.156515213333334</v>
+        <v>6.145156628333334</v>
       </c>
       <c r="Q74">
-        <v>10.42651521333333</v>
+        <v>10.41515662833333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.278158432271471</v>
+        <v>0.2858422428624588</v>
       </c>
       <c r="T74">
-        <v>1.620105821146938</v>
+        <v>1.673680749094919</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.527976041094973</v>
+        <v>8.411154451490933</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1045159055728639</v>
+        <v>0.1041834501097159</v>
       </c>
       <c r="C75">
-        <v>19.82981241982079</v>
+        <v>19.65336049856746</v>
       </c>
       <c r="D75">
-        <v>40.58071241982079</v>
+        <v>40.70756049856745</v>
       </c>
       <c r="E75">
-        <v>-3.859100000000002</v>
+        <v>-3.555800000000001</v>
       </c>
       <c r="F75">
-        <v>22.1409</v>
+        <v>22.4442</v>
       </c>
       <c r="G75">
         <v>1.39</v>
@@ -7431,28 +7431,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M75">
-        <v>1.18453815</v>
+        <v>1.2007647</v>
       </c>
       <c r="N75">
-        <v>8.778795183333333</v>
+        <v>8.762568633333332</v>
       </c>
       <c r="O75">
-        <v>2.633638555</v>
+        <v>2.62877059</v>
       </c>
       <c r="P75">
-        <v>6.145156628333334</v>
+        <v>6.133798043333332</v>
       </c>
       <c r="Q75">
-        <v>10.41515662833333</v>
+        <v>10.40379804333333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2858422428624588</v>
+        <v>0.2941171158065995</v>
       </c>
       <c r="T75">
-        <v>1.673680749094919</v>
+        <v>1.73137682534659</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>8.411154451490933</v>
+        <v>8.297490202146459</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1041834501097159</v>
+        <v>0.1038509946465679</v>
       </c>
       <c r="C76">
-        <v>19.65336049856746</v>
+        <v>19.4777040728913</v>
       </c>
       <c r="D76">
-        <v>40.70756049856745</v>
+        <v>40.83520407289129</v>
       </c>
       <c r="E76">
-        <v>-3.555800000000001</v>
+        <v>-3.252500000000001</v>
       </c>
       <c r="F76">
-        <v>22.4442</v>
+        <v>22.7475</v>
       </c>
       <c r="G76">
         <v>1.39</v>
@@ -7513,28 +7513,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M76">
-        <v>1.2007647</v>
+        <v>1.21699125</v>
       </c>
       <c r="N76">
-        <v>8.762568633333332</v>
+        <v>8.746342083333333</v>
       </c>
       <c r="O76">
-        <v>2.62877059</v>
+        <v>2.623902625</v>
       </c>
       <c r="P76">
-        <v>6.133798043333332</v>
+        <v>6.122439458333334</v>
       </c>
       <c r="Q76">
-        <v>10.40379804333333</v>
+        <v>10.39243945833333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2941171158065995</v>
+        <v>0.3030539785862715</v>
       </c>
       <c r="T76">
-        <v>1.73137682534659</v>
+        <v>1.793688587698396</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>8.297490202146459</v>
+        <v>8.186856999451173</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1038509946465679</v>
+        <v>0.1035185391834199</v>
       </c>
       <c r="C77">
-        <v>19.4777040728913</v>
+        <v>19.30285064945373</v>
       </c>
       <c r="D77">
-        <v>40.83520407289129</v>
+        <v>40.96365064945373</v>
       </c>
       <c r="E77">
-        <v>-3.252500000000001</v>
+        <v>-2.949200000000001</v>
       </c>
       <c r="F77">
-        <v>22.7475</v>
+        <v>23.0508</v>
       </c>
       <c r="G77">
         <v>1.39</v>
@@ -7595,28 +7595,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M77">
-        <v>1.21699125</v>
+        <v>1.2332178</v>
       </c>
       <c r="N77">
-        <v>8.746342083333333</v>
+        <v>8.730115533333333</v>
       </c>
       <c r="O77">
-        <v>2.623902625</v>
+        <v>2.61903466</v>
       </c>
       <c r="P77">
-        <v>6.122439458333334</v>
+        <v>6.111080873333333</v>
       </c>
       <c r="Q77">
-        <v>10.39243945833333</v>
+        <v>10.38108087333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3030539785862715</v>
+        <v>0.3127355799309161</v>
       </c>
       <c r="T77">
-        <v>1.793688587698396</v>
+        <v>1.861192996912852</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>8.186856999451173</v>
+        <v>8.079135196826817</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1035185391834199</v>
+        <v>0.1031860837202719</v>
       </c>
       <c r="C78">
-        <v>19.30285064945373</v>
+        <v>19.12880782966262</v>
       </c>
       <c r="D78">
-        <v>40.96365064945373</v>
+        <v>41.09290782966261</v>
       </c>
       <c r="E78">
-        <v>-2.949200000000001</v>
+        <v>-2.645900000000001</v>
       </c>
       <c r="F78">
-        <v>23.0508</v>
+        <v>23.3541</v>
       </c>
       <c r="G78">
         <v>1.39</v>
@@ -7677,28 +7677,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M78">
-        <v>1.2332178</v>
+        <v>1.24944435</v>
       </c>
       <c r="N78">
-        <v>8.730115533333333</v>
+        <v>8.713888983333334</v>
       </c>
       <c r="O78">
-        <v>2.61903466</v>
+        <v>2.614166695</v>
       </c>
       <c r="P78">
-        <v>6.111080873333333</v>
+        <v>6.099722288333334</v>
       </c>
       <c r="Q78">
-        <v>10.38108087333333</v>
+        <v>10.36972228833333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3127355799309161</v>
+        <v>0.3232590596533559</v>
       </c>
       <c r="T78">
-        <v>1.861192996912852</v>
+        <v>1.934567354754651</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>8.079135196826817</v>
+        <v>7.974211363101793</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1031860837202719</v>
+        <v>0.1028536282571239</v>
       </c>
       <c r="C79">
-        <v>19.12880782966262</v>
+        <v>18.95558331117175</v>
       </c>
       <c r="D79">
-        <v>41.09290782966261</v>
+        <v>41.22298331117175</v>
       </c>
       <c r="E79">
-        <v>-2.645900000000001</v>
+        <v>-2.342600000000001</v>
       </c>
       <c r="F79">
-        <v>23.3541</v>
+        <v>23.6574</v>
       </c>
       <c r="G79">
         <v>1.39</v>
@@ -7759,28 +7759,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M79">
-        <v>1.24944435</v>
+        <v>1.2656709</v>
       </c>
       <c r="N79">
-        <v>8.713888983333334</v>
+        <v>8.697662433333333</v>
       </c>
       <c r="O79">
-        <v>2.614166695</v>
+        <v>2.60929873</v>
       </c>
       <c r="P79">
-        <v>6.099722288333334</v>
+        <v>6.088363703333333</v>
       </c>
       <c r="Q79">
-        <v>10.36972228833333</v>
+        <v>10.35836370333333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3232590596533559</v>
+        <v>0.334739219350563</v>
       </c>
       <c r="T79">
-        <v>1.934567354754651</v>
+        <v>2.014612108763887</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.974211363101793</v>
+        <v>7.871977884087667</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1028536282571239</v>
+        <v>0.1025211727939758</v>
       </c>
       <c r="C80">
-        <v>18.95558331117175</v>
+        <v>18.78318488940907</v>
       </c>
       <c r="D80">
-        <v>41.22298331117175</v>
+        <v>41.35388488940907</v>
       </c>
       <c r="E80">
-        <v>-2.342600000000001</v>
+        <v>-2.039300000000001</v>
       </c>
       <c r="F80">
-        <v>23.6574</v>
+        <v>23.9607</v>
       </c>
       <c r="G80">
         <v>1.39</v>
@@ -7841,28 +7841,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M80">
-        <v>1.2656709</v>
+        <v>1.28189745</v>
       </c>
       <c r="N80">
-        <v>8.697662433333333</v>
+        <v>8.681435883333332</v>
       </c>
       <c r="O80">
-        <v>2.60929873</v>
+        <v>2.604430765</v>
       </c>
       <c r="P80">
-        <v>6.088363703333333</v>
+        <v>6.077005118333332</v>
       </c>
       <c r="Q80">
-        <v>10.35836370333333</v>
+        <v>10.34700511833333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.334739219350563</v>
+        <v>0.3473127275903612</v>
       </c>
       <c r="T80">
-        <v>2.014612108763887</v>
+        <v>2.102280172678765</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.871977884087667</v>
+        <v>7.772332594415671</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1025211727939758</v>
+        <v>0.1021887173308278</v>
       </c>
       <c r="C81">
-        <v>18.78318488940907</v>
+        <v>18.61162045913391</v>
       </c>
       <c r="D81">
-        <v>41.35388488940907</v>
+        <v>41.48562045913391</v>
       </c>
       <c r="E81">
-        <v>-2.039300000000001</v>
+        <v>-1.736000000000001</v>
       </c>
       <c r="F81">
-        <v>23.9607</v>
+        <v>24.264</v>
       </c>
       <c r="G81">
         <v>1.39</v>
@@ -7923,28 +7923,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M81">
-        <v>1.28189745</v>
+        <v>1.298124</v>
       </c>
       <c r="N81">
-        <v>8.681435883333332</v>
+        <v>8.665209333333333</v>
       </c>
       <c r="O81">
-        <v>2.604430765</v>
+        <v>2.5995628</v>
       </c>
       <c r="P81">
-        <v>6.077005118333332</v>
+        <v>6.065646533333334</v>
       </c>
       <c r="Q81">
-        <v>10.34700511833333</v>
+        <v>10.33564653333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3473127275903612</v>
+        <v>0.3611435866541393</v>
       </c>
       <c r="T81">
-        <v>2.102280172678765</v>
+        <v>2.198715042985131</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.772332594415671</v>
+        <v>7.675178436985476</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1021887173308278</v>
+        <v>0.1023098618676798</v>
       </c>
       <c r="C82">
-        <v>18.61162045913391</v>
+        <v>18.26021981935765</v>
       </c>
       <c r="D82">
-        <v>41.48562045913391</v>
+        <v>41.43751981935765</v>
       </c>
       <c r="E82">
-        <v>-1.736000000000001</v>
+        <v>-1.432700000000001</v>
       </c>
       <c r="F82">
-        <v>24.264</v>
+        <v>24.5673</v>
       </c>
       <c r="G82">
         <v>1.39</v>
@@ -8005,45 +8005,45 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M82">
-        <v>1.298124</v>
+        <v>1.33400439</v>
       </c>
       <c r="N82">
-        <v>8.665209333333333</v>
+        <v>8.629328943333332</v>
       </c>
       <c r="O82">
-        <v>2.5995628</v>
+        <v>2.588798683</v>
       </c>
       <c r="P82">
-        <v>6.065646533333334</v>
+        <v>6.040530260333332</v>
       </c>
       <c r="Q82">
-        <v>10.33564653333333</v>
+        <v>10.31053026033333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3611435866541393</v>
+        <v>0.3764303256193676</v>
       </c>
       <c r="T82">
-        <v>2.198715042985131</v>
+        <v>2.305300952271113</v>
       </c>
       <c r="U82">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V82">
         <v>0.3</v>
       </c>
       <c r="W82">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y82">
-        <v>7.675178436985476</v>
+        <v>7.468741038650804</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1023098618676798</v>
+        <v>0.1019830064045318</v>
       </c>
       <c r="C83">
-        <v>18.26021981935765</v>
+        <v>18.08695463723258</v>
       </c>
       <c r="D83">
-        <v>41.43751981935765</v>
+        <v>41.56755463723258</v>
       </c>
       <c r="E83">
-        <v>-1.432700000000001</v>
+        <v>-1.1294</v>
       </c>
       <c r="F83">
-        <v>24.5673</v>
+        <v>24.8706</v>
       </c>
       <c r="G83">
         <v>1.39</v>
@@ -8087,28 +8087,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M83">
-        <v>1.33400439</v>
+        <v>1.35047358</v>
       </c>
       <c r="N83">
-        <v>8.629328943333332</v>
+        <v>8.612859753333332</v>
       </c>
       <c r="O83">
-        <v>2.588798683</v>
+        <v>2.583857925999999</v>
       </c>
       <c r="P83">
-        <v>6.040530260333332</v>
+        <v>6.029001827333333</v>
       </c>
       <c r="Q83">
-        <v>10.31053026033333</v>
+        <v>10.29900182733333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3764303256193676</v>
+        <v>0.393415591136288</v>
       </c>
       <c r="T83">
-        <v>2.305300952271113</v>
+        <v>2.42372974036665</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.468741038650804</v>
+        <v>7.377658830862379</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1019830064045318</v>
+        <v>0.1016561509413838</v>
       </c>
       <c r="C84">
-        <v>18.08695463723258</v>
+        <v>17.91450814711255</v>
       </c>
       <c r="D84">
-        <v>41.56755463723258</v>
+        <v>41.69840814711254</v>
       </c>
       <c r="E84">
-        <v>-1.1294</v>
+        <v>-0.8261000000000003</v>
       </c>
       <c r="F84">
-        <v>24.8706</v>
+        <v>25.1739</v>
       </c>
       <c r="G84">
         <v>1.39</v>
@@ -8169,28 +8169,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M84">
-        <v>1.35047358</v>
+        <v>1.36694277</v>
       </c>
       <c r="N84">
-        <v>8.612859753333332</v>
+        <v>8.596390563333333</v>
       </c>
       <c r="O84">
-        <v>2.583857925999999</v>
+        <v>2.578917169</v>
       </c>
       <c r="P84">
-        <v>6.029001827333333</v>
+        <v>6.017473394333333</v>
       </c>
       <c r="Q84">
-        <v>10.29900182733333</v>
+        <v>10.28747339433333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.393415591136288</v>
+        <v>0.4123991231846109</v>
       </c>
       <c r="T84">
-        <v>2.42372974036665</v>
+        <v>2.556091327061662</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>7.377658830862379</v>
+        <v>7.288771375068857</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1016561509413838</v>
+        <v>0.1013292954782358</v>
       </c>
       <c r="C85">
-        <v>17.91450814711255</v>
+        <v>17.74288810507271</v>
       </c>
       <c r="D85">
-        <v>41.69840814711254</v>
+        <v>41.83008810507271</v>
       </c>
       <c r="E85">
-        <v>-0.8261000000000003</v>
+        <v>-0.5228000000000002</v>
       </c>
       <c r="F85">
-        <v>25.1739</v>
+        <v>25.4772</v>
       </c>
       <c r="G85">
         <v>1.39</v>
@@ -8251,28 +8251,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M85">
-        <v>1.36694277</v>
+        <v>1.38341196</v>
       </c>
       <c r="N85">
-        <v>8.596390563333333</v>
+        <v>8.579921373333333</v>
       </c>
       <c r="O85">
-        <v>2.578917169</v>
+        <v>2.573976412</v>
       </c>
       <c r="P85">
-        <v>6.017473394333333</v>
+        <v>6.005944961333332</v>
       </c>
       <c r="Q85">
-        <v>10.28747339433333</v>
+        <v>10.27594496133333</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4123991231846109</v>
+        <v>0.4337555967389741</v>
       </c>
       <c r="T85">
-        <v>2.556091327061662</v>
+        <v>2.70499811209355</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.288771375068857</v>
+        <v>7.202000287270418</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1013292954782358</v>
+        <v>0.1010024400150878</v>
       </c>
       <c r="C86">
-        <v>17.74288810507272</v>
+        <v>17.57210236547061</v>
       </c>
       <c r="D86">
-        <v>41.83008810507271</v>
+        <v>41.96260236547061</v>
       </c>
       <c r="E86">
-        <v>-0.5228000000000037</v>
+        <v>-0.2195000000000036</v>
       </c>
       <c r="F86">
-        <v>25.4772</v>
+        <v>25.7805</v>
       </c>
       <c r="G86">
         <v>1.39</v>
@@ -8333,28 +8333,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M86">
-        <v>1.38341196</v>
+        <v>1.39988115</v>
       </c>
       <c r="N86">
-        <v>8.579921373333333</v>
+        <v>8.563452183333332</v>
       </c>
       <c r="O86">
-        <v>2.573976412</v>
+        <v>2.569035655</v>
       </c>
       <c r="P86">
-        <v>6.005944961333332</v>
+        <v>5.994416528333333</v>
       </c>
       <c r="Q86">
-        <v>10.27594496133333</v>
+        <v>10.26441652833333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4337555967389738</v>
+        <v>0.4579596001005855</v>
       </c>
       <c r="T86">
-        <v>2.704998112093548</v>
+        <v>2.873759135129688</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>7.202000287270419</v>
+        <v>7.117270872126061</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1010024400150878</v>
+        <v>0.1006755845519398</v>
       </c>
       <c r="C87">
-        <v>17.57210236547061</v>
+        <v>17.4021588825079</v>
       </c>
       <c r="D87">
-        <v>41.96260236547061</v>
+        <v>42.0959588825079</v>
       </c>
       <c r="E87">
-        <v>-0.2195000000000036</v>
+        <v>0.08379999999999654</v>
       </c>
       <c r="F87">
-        <v>25.7805</v>
+        <v>26.0838</v>
       </c>
       <c r="G87">
         <v>1.39</v>
@@ -8415,28 +8415,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M87">
-        <v>1.39988115</v>
+        <v>1.41635034</v>
       </c>
       <c r="N87">
-        <v>8.563452183333332</v>
+        <v>8.546982993333334</v>
       </c>
       <c r="O87">
-        <v>2.569035655</v>
+        <v>2.564094898</v>
       </c>
       <c r="P87">
-        <v>5.994416528333333</v>
+        <v>5.982888095333333</v>
       </c>
       <c r="Q87">
-        <v>10.26441652833333</v>
+        <v>10.25288809533333</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4579596001005855</v>
+        <v>0.4856213182281415</v>
       </c>
       <c r="T87">
-        <v>2.873759135129688</v>
+        <v>3.066628875742418</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>7.117270872126061</v>
+        <v>7.034511908496689</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1006755845519398</v>
+        <v>0.1003487290887918</v>
       </c>
       <c r="C88">
-        <v>17.4021588825079</v>
+        <v>17.23306571182197</v>
       </c>
       <c r="D88">
-        <v>42.0959588825079</v>
+        <v>42.23016571182197</v>
       </c>
       <c r="E88">
-        <v>0.08379999999999654</v>
+        <v>0.3870999999999967</v>
       </c>
       <c r="F88">
-        <v>26.0838</v>
+        <v>26.3871</v>
       </c>
       <c r="G88">
         <v>1.39</v>
@@ -8497,28 +8497,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M88">
-        <v>1.41635034</v>
+        <v>1.43281953</v>
       </c>
       <c r="N88">
-        <v>8.546982993333334</v>
+        <v>8.530513803333333</v>
       </c>
       <c r="O88">
-        <v>2.564094898</v>
+        <v>2.559154141</v>
       </c>
       <c r="P88">
-        <v>5.982888095333333</v>
+        <v>5.971359662333333</v>
       </c>
       <c r="Q88">
-        <v>10.25288809533333</v>
+        <v>10.24135966233333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4856213182281415</v>
+        <v>0.5175386852983985</v>
       </c>
       <c r="T88">
-        <v>3.066628875742418</v>
+        <v>3.289170884141723</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>7.034511908496689</v>
+        <v>6.953655449778336</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1003487290887918</v>
+        <v>0.1000218736256438</v>
       </c>
       <c r="C89">
-        <v>17.23306571182197</v>
+        <v>17.06483101210796</v>
       </c>
       <c r="D89">
-        <v>42.23016571182197</v>
+        <v>42.36523101210796</v>
       </c>
       <c r="E89">
-        <v>0.3870999999999967</v>
+        <v>0.6904000000000003</v>
       </c>
       <c r="F89">
-        <v>26.3871</v>
+        <v>26.6904</v>
       </c>
       <c r="G89">
         <v>1.39</v>
@@ -8579,28 +8579,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M89">
-        <v>1.43281953</v>
+        <v>1.44928872</v>
       </c>
       <c r="N89">
-        <v>8.530513803333333</v>
+        <v>8.514044613333333</v>
       </c>
       <c r="O89">
-        <v>2.559154141</v>
+        <v>2.554213384</v>
       </c>
       <c r="P89">
-        <v>5.971359662333333</v>
+        <v>5.959831229333333</v>
       </c>
       <c r="Q89">
-        <v>10.24135966233333</v>
+        <v>10.22983122933333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5175386852983985</v>
+        <v>0.5547756135470318</v>
       </c>
       <c r="T89">
-        <v>3.289170884141723</v>
+        <v>3.548803227274246</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.953655449778336</v>
+        <v>6.874636637849036</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1000218736256438</v>
+        <v>0.09969501816249579</v>
       </c>
       <c r="C90">
-        <v>17.06483101210796</v>
+        <v>16.89746304677221</v>
       </c>
       <c r="D90">
-        <v>42.36523101210796</v>
+        <v>42.50116304677221</v>
       </c>
       <c r="E90">
-        <v>0.6904000000000003</v>
+        <v>0.9937000000000005</v>
       </c>
       <c r="F90">
-        <v>26.6904</v>
+        <v>26.9937</v>
       </c>
       <c r="G90">
         <v>1.39</v>
@@ -8661,28 +8661,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M90">
-        <v>1.44928872</v>
+        <v>1.46575791</v>
       </c>
       <c r="N90">
-        <v>8.514044613333333</v>
+        <v>8.497575423333332</v>
       </c>
       <c r="O90">
-        <v>2.554213384</v>
+        <v>2.549272627</v>
       </c>
       <c r="P90">
-        <v>5.959831229333333</v>
+        <v>5.948302796333333</v>
       </c>
       <c r="Q90">
-        <v>10.22983122933333</v>
+        <v>10.21830279633333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5547756135470318</v>
+        <v>0.5987828923863254</v>
       </c>
       <c r="T90">
-        <v>3.548803227274246</v>
+        <v>3.855641450976317</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.874636637849036</v>
+        <v>6.797393529558597</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09969501816249579</v>
+        <v>0.09936816269934778</v>
       </c>
       <c r="C91">
-        <v>16.89746304677221</v>
+        <v>16.73097018561745</v>
       </c>
       <c r="D91">
-        <v>42.50116304677221</v>
+        <v>42.63797018561745</v>
       </c>
       <c r="E91">
-        <v>0.9937000000000005</v>
+        <v>1.297000000000001</v>
       </c>
       <c r="F91">
-        <v>26.9937</v>
+        <v>27.297</v>
       </c>
       <c r="G91">
         <v>1.39</v>
@@ -8743,28 +8743,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M91">
-        <v>1.46575791</v>
+        <v>1.4822271</v>
       </c>
       <c r="N91">
-        <v>8.497575423333332</v>
+        <v>8.481106233333334</v>
       </c>
       <c r="O91">
-        <v>2.549272627</v>
+        <v>2.54433187</v>
       </c>
       <c r="P91">
-        <v>5.948302796333333</v>
+        <v>5.936774363333333</v>
       </c>
       <c r="Q91">
-        <v>10.21830279633333</v>
+        <v>10.20677436333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5987828923863254</v>
+        <v>0.6515916269934781</v>
       </c>
       <c r="T91">
-        <v>3.855641450976317</v>
+        <v>4.223847319418804</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.797393529558597</v>
+        <v>6.721866934785725</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09936816269934778</v>
+        <v>0.09904130723619978</v>
       </c>
       <c r="C92">
-        <v>16.73097018561745</v>
+        <v>16.56536090656081</v>
       </c>
       <c r="D92">
-        <v>42.63797018561745</v>
+        <v>42.77566090656081</v>
       </c>
       <c r="E92">
-        <v>1.297000000000001</v>
+        <v>1.600300000000001</v>
       </c>
       <c r="F92">
-        <v>27.297</v>
+        <v>27.6003</v>
       </c>
       <c r="G92">
         <v>1.39</v>
@@ -8825,28 +8825,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M92">
-        <v>1.4822271</v>
+        <v>1.49869629</v>
       </c>
       <c r="N92">
-        <v>8.481106233333334</v>
+        <v>8.464637043333333</v>
       </c>
       <c r="O92">
-        <v>2.54433187</v>
+        <v>2.539391113</v>
       </c>
       <c r="P92">
-        <v>5.936774363333333</v>
+        <v>5.925245930333333</v>
       </c>
       <c r="Q92">
-        <v>10.20677436333333</v>
+        <v>10.19524593033333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6515916269934781</v>
+        <v>0.7161356359577756</v>
       </c>
       <c r="T92">
-        <v>4.223847319418804</v>
+        <v>4.673876714181842</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.721866934785725</v>
+        <v>6.648000265172694</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09904130723619978</v>
+        <v>0.09871445177305177</v>
       </c>
       <c r="C93">
-        <v>16.56536090656081</v>
+        <v>16.40064379738505</v>
       </c>
       <c r="D93">
-        <v>42.77566090656081</v>
+        <v>42.91424379738505</v>
       </c>
       <c r="E93">
-        <v>1.600300000000001</v>
+        <v>1.903600000000001</v>
       </c>
       <c r="F93">
-        <v>27.6003</v>
+        <v>27.9036</v>
       </c>
       <c r="G93">
         <v>1.39</v>
@@ -8907,28 +8907,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M93">
-        <v>1.49869629</v>
+        <v>1.51516548</v>
       </c>
       <c r="N93">
-        <v>8.464637043333333</v>
+        <v>8.448167853333333</v>
       </c>
       <c r="O93">
-        <v>2.539391113</v>
+        <v>2.534450356</v>
       </c>
       <c r="P93">
-        <v>5.925245930333333</v>
+        <v>5.913717497333333</v>
       </c>
       <c r="Q93">
-        <v>10.19524593033333</v>
+        <v>10.18371749733333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7161356359577756</v>
+        <v>0.7968156471631477</v>
       </c>
       <c r="T93">
-        <v>4.673876714181842</v>
+        <v>5.236413457635642</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.648000265172694</v>
+        <v>6.575739392725165</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09871445177305177</v>
+        <v>0.09838759630990378</v>
       </c>
       <c r="C94">
-        <v>16.40064379738505</v>
+        <v>16.23682755752412</v>
       </c>
       <c r="D94">
-        <v>42.91424379738505</v>
+        <v>43.05372755752412</v>
       </c>
       <c r="E94">
-        <v>1.903600000000001</v>
+        <v>2.206900000000001</v>
       </c>
       <c r="F94">
-        <v>27.9036</v>
+        <v>28.2069</v>
       </c>
       <c r="G94">
         <v>1.39</v>
@@ -8989,28 +8989,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M94">
-        <v>1.51516548</v>
+        <v>1.53163467</v>
       </c>
       <c r="N94">
-        <v>8.448167853333333</v>
+        <v>8.431698663333332</v>
       </c>
       <c r="O94">
-        <v>2.534450356</v>
+        <v>2.529509598999999</v>
       </c>
       <c r="P94">
-        <v>5.913717497333333</v>
+        <v>5.902189064333333</v>
       </c>
       <c r="Q94">
-        <v>10.18371749733333</v>
+        <v>10.17218906433333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7968156471631477</v>
+        <v>0.9005470901414832</v>
       </c>
       <c r="T94">
-        <v>5.236413457635642</v>
+        <v>5.959674984933383</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.575739392725165</v>
+        <v>6.505032517534571</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09838759630990378</v>
+        <v>0.09806074084675577</v>
       </c>
       <c r="C95">
-        <v>16.23682755752412</v>
+        <v>16.07392099988352</v>
       </c>
       <c r="D95">
-        <v>43.05372755752412</v>
+        <v>43.19412099988352</v>
       </c>
       <c r="E95">
-        <v>2.206900000000001</v>
+        <v>2.510200000000001</v>
       </c>
       <c r="F95">
-        <v>28.2069</v>
+        <v>28.5102</v>
       </c>
       <c r="G95">
         <v>1.39</v>
@@ -9071,28 +9071,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M95">
-        <v>1.53163467</v>
+        <v>1.54810386</v>
       </c>
       <c r="N95">
-        <v>8.431698663333332</v>
+        <v>8.415229473333333</v>
       </c>
       <c r="O95">
-        <v>2.529509598999999</v>
+        <v>2.524568842</v>
       </c>
       <c r="P95">
-        <v>5.902189064333333</v>
+        <v>5.890660631333334</v>
       </c>
       <c r="Q95">
-        <v>10.17218906433333</v>
+        <v>10.16066063133333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9005470901414832</v>
+        <v>1.038855680779264</v>
       </c>
       <c r="T95">
-        <v>5.959674984933383</v>
+        <v>6.92402368799704</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>6.505032517534571</v>
+        <v>6.435830043943779</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09806074084675577</v>
+        <v>0.09773388538360778</v>
       </c>
       <c r="C96">
-        <v>16.07392099988352</v>
+        <v>15.91193305269649</v>
       </c>
       <c r="D96">
-        <v>43.19412099988352</v>
+        <v>43.33543305269649</v>
       </c>
       <c r="E96">
-        <v>2.510200000000001</v>
+        <v>2.813500000000001</v>
       </c>
       <c r="F96">
-        <v>28.5102</v>
+        <v>28.8135</v>
       </c>
       <c r="G96">
         <v>1.39</v>
@@ -9153,28 +9153,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M96">
-        <v>1.54810386</v>
+        <v>1.56457305</v>
       </c>
       <c r="N96">
-        <v>8.415229473333333</v>
+        <v>8.398760283333333</v>
       </c>
       <c r="O96">
-        <v>2.524568842</v>
+        <v>2.519628085</v>
       </c>
       <c r="P96">
-        <v>5.890660631333334</v>
+        <v>5.879132198333333</v>
       </c>
       <c r="Q96">
-        <v>10.16066063133333</v>
+        <v>10.14913219833333</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.038855680779264</v>
+        <v>1.232487707672157</v>
       </c>
       <c r="T96">
-        <v>6.92402368799704</v>
+        <v>8.274111872286159</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.435830043943779</v>
+        <v>6.368084464533844</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09773388538360778</v>
+        <v>0.09740702992045977</v>
       </c>
       <c r="C97">
-        <v>15.91193305269649</v>
+        <v>15.75087276141663</v>
       </c>
       <c r="D97">
-        <v>43.33543305269649</v>
+        <v>43.47767276141663</v>
       </c>
       <c r="E97">
-        <v>2.813500000000001</v>
+        <v>3.116800000000001</v>
       </c>
       <c r="F97">
-        <v>28.8135</v>
+        <v>29.1168</v>
       </c>
       <c r="G97">
         <v>1.39</v>
@@ -9235,28 +9235,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M97">
-        <v>1.56457305</v>
+        <v>1.58104224</v>
       </c>
       <c r="N97">
-        <v>8.398760283333333</v>
+        <v>8.382291093333333</v>
       </c>
       <c r="O97">
-        <v>2.519628085</v>
+        <v>2.514687327999999</v>
       </c>
       <c r="P97">
-        <v>5.879132198333333</v>
+        <v>5.867603765333333</v>
       </c>
       <c r="Q97">
-        <v>10.14913219833333</v>
+        <v>10.13760376533333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.232487707672157</v>
+        <v>1.522935748011497</v>
       </c>
       <c r="T97">
-        <v>8.274111872286159</v>
+        <v>10.29924414871984</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>6.368084464533844</v>
+        <v>6.301750251361615</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09740702992045977</v>
+        <v>0.09708017445731176</v>
       </c>
       <c r="C98">
-        <v>15.75087276141664</v>
+        <v>15.59074929064808</v>
       </c>
       <c r="D98">
-        <v>43.47767276141663</v>
+        <v>43.62084929064808</v>
       </c>
       <c r="E98">
-        <v>3.116799999999998</v>
+        <v>3.420099999999998</v>
       </c>
       <c r="F98">
-        <v>29.1168</v>
+        <v>29.4201</v>
       </c>
       <c r="G98">
         <v>1.39</v>
@@ -9317,28 +9317,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M98">
-        <v>1.58104224</v>
+        <v>1.59751143</v>
       </c>
       <c r="N98">
-        <v>8.382291093333333</v>
+        <v>8.365821903333334</v>
       </c>
       <c r="O98">
-        <v>2.514687327999999</v>
+        <v>2.509746571</v>
       </c>
       <c r="P98">
-        <v>5.867603765333333</v>
+        <v>5.856075332333334</v>
       </c>
       <c r="Q98">
-        <v>10.13760376533333</v>
+        <v>10.12607533233333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.522935748011493</v>
+        <v>2.007015815243724</v>
       </c>
       <c r="T98">
-        <v>10.29924414871981</v>
+        <v>13.6744646094426</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>6.301750251361616</v>
+        <v>6.236783753924899</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09708017445731176</v>
+        <v>0.09675331899416376</v>
       </c>
       <c r="C99">
-        <v>15.59074929064808</v>
+        <v>15.43157192611385</v>
       </c>
       <c r="D99">
-        <v>43.62084929064808</v>
+        <v>43.76497192611384</v>
       </c>
       <c r="E99">
-        <v>3.420099999999998</v>
+        <v>3.723399999999998</v>
       </c>
       <c r="F99">
-        <v>29.4201</v>
+        <v>29.7234</v>
       </c>
       <c r="G99">
         <v>1.39</v>
@@ -9399,28 +9399,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M99">
-        <v>1.59751143</v>
+        <v>1.61398062</v>
       </c>
       <c r="N99">
-        <v>8.365821903333334</v>
+        <v>8.349352713333333</v>
       </c>
       <c r="O99">
-        <v>2.509746571</v>
+        <v>2.504805814</v>
       </c>
       <c r="P99">
-        <v>5.856075332333334</v>
+        <v>5.844546899333333</v>
       </c>
       <c r="Q99">
-        <v>10.12607533233333</v>
+        <v>10.11454689933333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.007015815243724</v>
+        <v>2.975175949708186</v>
       </c>
       <c r="T99">
-        <v>13.6744646094426</v>
+        <v>20.42490553088817</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>6.236783753924899</v>
+        <v>6.173143103374645</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09675331899416376</v>
+        <v>0.09642646353101575</v>
       </c>
       <c r="C100">
-        <v>15.43157192611385</v>
+        <v>15.27335007666326</v>
       </c>
       <c r="D100">
-        <v>43.76497192611384</v>
+        <v>43.91005007666325</v>
       </c>
       <c r="E100">
-        <v>3.723399999999998</v>
+        <v>4.026699999999998</v>
       </c>
       <c r="F100">
-        <v>29.7234</v>
+        <v>30.0267</v>
       </c>
       <c r="G100">
         <v>1.39</v>
@@ -9481,28 +9481,28 @@
         <v>9.963333333333333</v>
       </c>
       <c r="M100">
-        <v>1.61398062</v>
+        <v>1.63044981</v>
       </c>
       <c r="N100">
-        <v>8.349352713333333</v>
+        <v>8.332883523333333</v>
       </c>
       <c r="O100">
-        <v>2.504805814</v>
+        <v>2.499865057</v>
       </c>
       <c r="P100">
-        <v>5.844546899333333</v>
+        <v>5.833018466333334</v>
       </c>
       <c r="Q100">
-        <v>10.11454689933333</v>
+        <v>10.10301846633333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.975175949708186</v>
+        <v>5.87965635310157</v>
       </c>
       <c r="T100">
-        <v>20.42490553088817</v>
+        <v>40.67622829522487</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>6.173143103374645</v>
+        <v>6.110788122532476</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09642646353101575</v>
-      </c>
-      <c r="C101">
-        <v>15.27335007666326</v>
-      </c>
-      <c r="D101">
-        <v>43.91005007666325</v>
-      </c>
-      <c r="E101">
-        <v>4.026699999999998</v>
-      </c>
-      <c r="F101">
-        <v>30.0267</v>
-      </c>
-      <c r="G101">
-        <v>1.39</v>
-      </c>
-      <c r="H101">
-        <v>4.33</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.23333333333333</v>
-      </c>
-      <c r="K101">
-        <v>4.27</v>
-      </c>
-      <c r="L101">
-        <v>9.963333333333333</v>
-      </c>
-      <c r="M101">
-        <v>1.63044981</v>
-      </c>
-      <c r="N101">
-        <v>8.332883523333333</v>
-      </c>
-      <c r="O101">
-        <v>2.499865057</v>
-      </c>
-      <c r="P101">
-        <v>5.833018466333334</v>
-      </c>
-      <c r="Q101">
-        <v>10.10301846633333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.87965635310157</v>
-      </c>
-      <c r="T101">
-        <v>40.67622829522487</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03801</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>6.110788122532476</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
